--- a/public/exports/29189374.xlsx
+++ b/public/exports/29189374.xlsx
@@ -181,7 +181,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">100447736</t>
+          <t xml:space="preserve">100298242, 100298243</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -190,7 +190,7 @@
         </is>
       </c>
       <c r="F4">
-        <v>974</v>
+        <v>2442</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -231,16 +231,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">100450727</t>
+          <t xml:space="preserve">100447736</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F5">
-        <v>1399</v>
+        <v>974</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -281,16 +281,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2211891</t>
+          <t xml:space="preserve">100450727</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F6">
-        <v>583</v>
+        <v>1399</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -331,16 +331,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2215474</t>
+          <t xml:space="preserve">2211891</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F7">
-        <v>311</v>
+        <v>583</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -381,16 +381,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2215682</t>
+          <t xml:space="preserve">2215474</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F8">
-        <v>490</v>
+        <v>311</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -436,11 +436,11 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F9">
-        <v>252</v>
+        <v>490</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -481,16 +481,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2216228</t>
+          <t xml:space="preserve">2215682</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F10">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -536,7 +536,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F11">
@@ -581,16 +581,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2220022</t>
+          <t xml:space="preserve">2216228</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F12">
-        <v>299</v>
+        <v>259</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -631,16 +631,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2589978</t>
+          <t xml:space="preserve">2220022</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F13">
-        <v>252</v>
+        <v>299</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -681,16 +681,16 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2592022</t>
+          <t xml:space="preserve">2597454</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F14">
-        <v>264</v>
+        <v>443</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -731,16 +731,16 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2595904</t>
+          <t xml:space="preserve">265067, 265068</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F15">
-        <v>650</v>
+        <v>2578</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -781,16 +781,16 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2597454</t>
+          <t xml:space="preserve">265103</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F16">
-        <v>443</v>
+        <v>298</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -831,16 +831,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298996</t>
+          <t xml:space="preserve">266956, 266957</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F17">
-        <v>1261</v>
+        <v>7502</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -881,16 +881,16 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298996</t>
+          <t xml:space="preserve">266956, 266958</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F18">
-        <v>2331</v>
+        <v>4799</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298996</t>
+          <t xml:space="preserve">268650, 268651</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F19">
-        <v>346</v>
+        <v>1122</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5300078</t>
+          <t xml:space="preserve">268651</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="F20">
-        <v>1287</v>
+        <v>602</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1031,16 +1031,16 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5301218</t>
+          <t xml:space="preserve">268652, 268653</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F21">
-        <v>891</v>
+        <v>2677</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1081,16 +1081,16 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5301281</t>
+          <t xml:space="preserve">269957, 269958</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F22">
-        <v>577</v>
+        <v>2042</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1131,16 +1131,16 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5301281</t>
+          <t xml:space="preserve">271380, 271381</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F23">
-        <v>340</v>
+        <v>1104</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1181,16 +1181,16 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">5301893</t>
+          <t xml:space="preserve">5298996</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F24">
-        <v>981</v>
+        <v>1261</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1231,16 +1231,16 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5301893</t>
+          <t xml:space="preserve">5298996</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F25">
-        <v>816</v>
+        <v>2331</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1281,16 +1281,16 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5301893</t>
+          <t xml:space="preserve">5298996</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F26">
-        <v>918</v>
+        <v>346</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1331,16 +1331,16 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5301893</t>
+          <t xml:space="preserve">5300078</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F27">
-        <v>808</v>
+        <v>1287</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5302896</t>
+          <t xml:space="preserve">5301218</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F28">
-        <v>395</v>
+        <v>891</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1431,16 +1431,16 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">718738, 2594250</t>
+          <t xml:space="preserve">5301281</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F29">
-        <v>1898</v>
+        <v>577</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1481,16 +1481,16 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">718828, 2594249</t>
+          <t xml:space="preserve">5301281</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F30">
-        <v>1067</v>
+        <v>340</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1531,16 +1531,16 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">718829, 2594250</t>
+          <t xml:space="preserve">5301893</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F31">
-        <v>3072</v>
+        <v>981</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1581,16 +1581,16 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">718836, 5300194</t>
+          <t xml:space="preserve">5301893</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F32">
-        <v>467</v>
+        <v>816</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1631,16 +1631,16 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">718839, 5300196</t>
+          <t xml:space="preserve">5301893</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F33">
-        <v>300</v>
+        <v>918</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1681,16 +1681,16 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">718840, 5300198</t>
+          <t xml:space="preserve">5301893</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F34">
-        <v>300</v>
+        <v>808</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1731,16 +1731,16 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">718841, 5300199</t>
+          <t xml:space="preserve">5302896</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F35">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1781,16 +1781,16 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">718843, 5300201</t>
+          <t xml:space="preserve">718738, 2594250</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F36">
-        <v>400</v>
+        <v>1898</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1831,16 +1831,16 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">718862, 5300213</t>
+          <t xml:space="preserve">718828, 2594249</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F37">
-        <v>300</v>
+        <v>1067</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1881,16 +1881,16 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">718875, 2214316</t>
+          <t xml:space="preserve">718836, 5300194</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F38">
-        <v>2158</v>
+        <v>467</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1931,16 +1931,16 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">718877, 2595511</t>
+          <t xml:space="preserve">718839, 5300196</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F39">
-        <v>3030</v>
+        <v>300</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1981,16 +1981,16 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">7781206</t>
+          <t xml:space="preserve">718840, 5300198</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F40">
-        <v>1240</v>
+        <v>300</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2031,16 +2031,16 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">8314669</t>
+          <t xml:space="preserve">718843, 5300201</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="F41">
-        <v>259</v>
+        <v>400</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2081,16 +2081,16 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">8314669</t>
+          <t xml:space="preserve">7781206</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F42">
-        <v>259</v>
+        <v>1240</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">8314712</t>
+          <t xml:space="preserve">8314669</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="F43">
-        <v>285</v>
+        <v>259</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">8314761, 100794736</t>
+          <t xml:space="preserve">8314669</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="F44">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">8314857</t>
+          <t xml:space="preserve">8314712</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="F45">
-        <v>387</v>
+        <v>285</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">8314857</t>
+          <t xml:space="preserve">8314761, 100794736</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="F46">
-        <v>1222</v>
+        <v>262</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2336,11 +2336,11 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F47">
-        <v>271</v>
+        <v>387</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2381,16 +2381,16 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">8765343</t>
+          <t xml:space="preserve">8314857</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F48">
-        <v>2988</v>
+        <v>1222</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2431,16 +2431,16 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">8765343</t>
+          <t xml:space="preserve">8314857</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F49">
-        <v>2512</v>
+        <v>271</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2486,11 +2486,11 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F50">
-        <v>1540</v>
+        <v>2988</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2536,11 +2536,11 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F51">
-        <v>2844</v>
+        <v>2512</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2586,11 +2586,11 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F52">
-        <v>1874</v>
+        <v>1540</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2631,16 +2631,16 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">8769222</t>
+          <t xml:space="preserve">8765343</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F53">
-        <v>987</v>
+        <v>2844</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2681,16 +2681,16 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940960</t>
+          <t xml:space="preserve">8765343</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F54">
-        <v>305</v>
+        <v>1874</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2731,16 +2731,16 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940960</t>
+          <t xml:space="preserve">8769222</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F55">
-        <v>595</v>
+        <v>987</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2786,11 +2786,11 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F56">
-        <v>637</v>
+        <v>305</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2836,11 +2836,11 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F57">
-        <v>699</v>
+        <v>595</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2881,30 +2881,30 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209946</t>
+          <t xml:space="preserve">8940960</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F58">
-        <v>286</v>
+        <v>637</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">200037910</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-27</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -2931,30 +2931,30 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">269957, 269958</t>
+          <t xml:space="preserve">8940960</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F59">
-        <v>2042</v>
+        <v>699</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311067567</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-08-08</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -2981,25 +2981,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">9517472</t>
+          <t xml:space="preserve">718862, 5300213</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F60">
-        <v>3416</v>
+        <v>300</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311067575</t>
+          <t xml:space="preserve">200000890</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-08-08</t>
+          <t xml:space="preserve">2014-04-22</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3031,25 +3031,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">9517473</t>
+          <t xml:space="preserve">718875, 2214316</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F61">
-        <v>3416</v>
+        <v>2158</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311067568</t>
+          <t xml:space="preserve">310015406</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-08-08</t>
+          <t xml:space="preserve">2022-11-29</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3081,25 +3081,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2592022</t>
+          <t xml:space="preserve">718829, 2594250</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F62">
-        <v>699</v>
+        <v>3072</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311165257</t>
+          <t xml:space="preserve">310023399</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-17</t>
+          <t xml:space="preserve">2023-02-04</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">100090478</t>
+          <t xml:space="preserve">718877, 2595511</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3140,26 +3140,26 @@
         </is>
       </c>
       <c r="F63">
-        <v>2788</v>
+        <v>3030</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311317744</t>
+          <t xml:space="preserve">310023400</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-31</t>
+          <t xml:space="preserve">2023-02-04</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -3181,35 +3181,35 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5302948</t>
+          <t xml:space="preserve">9517472</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F64">
-        <v>642</v>
+        <v>3416</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311408662</t>
+          <t xml:space="preserve">311067575</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-13</t>
+          <t xml:space="preserve">2024-08-08</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2591592</t>
+          <t xml:space="preserve">9517473</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3240,26 +3240,26 @@
         </is>
       </c>
       <c r="F65">
-        <v>1453</v>
+        <v>3416</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311461620</t>
+          <t xml:space="preserve">311067568</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-17</t>
+          <t xml:space="preserve">2024-08-08</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -3281,35 +3281,35 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2591592</t>
+          <t xml:space="preserve">2592022</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F66">
-        <v>628</v>
+        <v>699</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311461620</t>
+          <t xml:space="preserve">311165256</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-17</t>
+          <t xml:space="preserve">2026-03-17</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -3331,35 +3331,35 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2596007</t>
+          <t xml:space="preserve">2592022</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F67">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311461664</t>
+          <t xml:space="preserve">311165256</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-17</t>
+          <t xml:space="preserve">2026-03-17</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -3381,25 +3381,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">5299989</t>
+          <t xml:space="preserve">718841, 5300199</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="F68">
-        <v>1278</v>
+        <v>393</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311461719</t>
+          <t xml:space="preserve">311228167</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-17</t>
+          <t xml:space="preserve">2027-02-13</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3431,25 +3431,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">100000634</t>
+          <t xml:space="preserve">5302948</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F69">
-        <v>840</v>
+        <v>642</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311461926</t>
+          <t xml:space="preserve">311408662</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-18</t>
+          <t xml:space="preserve">2029-11-13</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2219478</t>
+          <t xml:space="preserve">2591592</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3490,16 +3490,16 @@
         </is>
       </c>
       <c r="F70">
-        <v>383</v>
+        <v>1453</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311461925</t>
+          <t xml:space="preserve">311461620</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-18</t>
+          <t xml:space="preserve">2030-09-17</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3531,25 +3531,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2219384</t>
+          <t xml:space="preserve">2591592</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F71">
-        <v>367</v>
+        <v>628</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311462237</t>
+          <t xml:space="preserve">311461620</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-21</t>
+          <t xml:space="preserve">2030-09-17</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3581,25 +3581,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2595275</t>
+          <t xml:space="preserve">2596007</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F72">
-        <v>470</v>
+        <v>252</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466054</t>
+          <t xml:space="preserve">311461664</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-08</t>
+          <t xml:space="preserve">2030-09-17</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298693</t>
+          <t xml:space="preserve">5299989</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3640,16 +3640,16 @@
         </is>
       </c>
       <c r="F73">
-        <v>325</v>
+        <v>1278</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311468126</t>
+          <t xml:space="preserve">311461719</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-20</t>
+          <t xml:space="preserve">2030-09-17</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3681,25 +3681,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2595274</t>
+          <t xml:space="preserve">100000634</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F74">
-        <v>379</v>
+        <v>840</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311469400</t>
+          <t xml:space="preserve">311461926</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-23</t>
+          <t xml:space="preserve">2030-09-18</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">5299172</t>
+          <t xml:space="preserve">2219478</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3740,16 +3740,16 @@
         </is>
       </c>
       <c r="F75">
-        <v>877</v>
+        <v>383</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311469402</t>
+          <t xml:space="preserve">311461925</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-23</t>
+          <t xml:space="preserve">2030-09-18</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3781,25 +3781,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">5299172</t>
+          <t xml:space="preserve">2219384</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F76">
-        <v>282</v>
+        <v>367</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311469399</t>
+          <t xml:space="preserve">311462237</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-23</t>
+          <t xml:space="preserve">2030-09-21</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3836,20 +3836,20 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F77">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474129</t>
+          <t xml:space="preserve">311466054</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-09</t>
+          <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">5302760</t>
+          <t xml:space="preserve">5298693</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3890,16 +3890,16 @@
         </is>
       </c>
       <c r="F78">
-        <v>597</v>
+        <v>325</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474331</t>
+          <t xml:space="preserve">311468126</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-10</t>
+          <t xml:space="preserve">2030-10-20</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">5302764</t>
+          <t xml:space="preserve">2595274</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3940,16 +3940,16 @@
         </is>
       </c>
       <c r="F79">
-        <v>1199</v>
+        <v>379</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474762</t>
+          <t xml:space="preserve">311469400</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-11</t>
+          <t xml:space="preserve">2030-10-23</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2215847</t>
+          <t xml:space="preserve">5299172</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3990,16 +3990,16 @@
         </is>
       </c>
       <c r="F80">
-        <v>552</v>
+        <v>877</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475459</t>
+          <t xml:space="preserve">311469402</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-13</t>
+          <t xml:space="preserve">2030-10-23</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4031,25 +4031,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2593903</t>
+          <t xml:space="preserve">5299172</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F81">
-        <v>722</v>
+        <v>282</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475469</t>
+          <t xml:space="preserve">311469399</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-13</t>
+          <t xml:space="preserve">2030-10-23</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2594914</t>
+          <t xml:space="preserve">2595275</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="F82">
-        <v>442</v>
+        <v>503</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475465</t>
+          <t xml:space="preserve">311474129</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-13</t>
+          <t xml:space="preserve">2030-11-09</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4131,25 +4131,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2594914</t>
+          <t xml:space="preserve">5302760</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F83">
-        <v>502</v>
+        <v>597</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475465</t>
+          <t xml:space="preserve">311474331</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-13</t>
+          <t xml:space="preserve">2030-11-10</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298850</t>
+          <t xml:space="preserve">5302764</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4190,16 +4190,16 @@
         </is>
       </c>
       <c r="F84">
-        <v>321</v>
+        <v>1199</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475476</t>
+          <t xml:space="preserve">311474762</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-13</t>
+          <t xml:space="preserve">2030-11-11</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">5299044</t>
+          <t xml:space="preserve">2215847</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4240,11 +4240,11 @@
         </is>
       </c>
       <c r="F85">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475426</t>
+          <t xml:space="preserve">311475459</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">5299241</t>
+          <t xml:space="preserve">2593903</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4290,11 +4290,11 @@
         </is>
       </c>
       <c r="F86">
-        <v>734</v>
+        <v>722</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475433</t>
+          <t xml:space="preserve">311475469</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">5302763</t>
+          <t xml:space="preserve">2594914</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4340,11 +4340,11 @@
         </is>
       </c>
       <c r="F87">
-        <v>1324</v>
+        <v>442</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475438</t>
+          <t xml:space="preserve">311475465</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4381,25 +4381,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">8638680</t>
+          <t xml:space="preserve">2594914</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F88">
-        <v>465</v>
+        <v>502</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475851</t>
+          <t xml:space="preserve">311475465</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-16</t>
+          <t xml:space="preserve">2030-11-13</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">9370842</t>
+          <t xml:space="preserve">5298850</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4440,16 +4440,16 @@
         </is>
       </c>
       <c r="F89">
-        <v>784</v>
+        <v>321</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475844</t>
+          <t xml:space="preserve">311475476</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-16</t>
+          <t xml:space="preserve">2030-11-13</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2597534</t>
+          <t xml:space="preserve">5299044</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4490,16 +4490,16 @@
         </is>
       </c>
       <c r="F90">
-        <v>600</v>
+        <v>557</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311476529</t>
+          <t xml:space="preserve">311475426</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-18</t>
+          <t xml:space="preserve">2030-11-13</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4531,25 +4531,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2597534</t>
+          <t xml:space="preserve">5299241</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F91">
-        <v>948</v>
+        <v>734</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311476529</t>
+          <t xml:space="preserve">311475433</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-18</t>
+          <t xml:space="preserve">2030-11-13</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">7010687</t>
+          <t xml:space="preserve">5302763</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4590,16 +4590,16 @@
         </is>
       </c>
       <c r="F92">
-        <v>722</v>
+        <v>1324</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311477758</t>
+          <t xml:space="preserve">311475438</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-23</t>
+          <t xml:space="preserve">2030-11-13</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">5299224</t>
+          <t xml:space="preserve">8638680</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4640,16 +4640,16 @@
         </is>
       </c>
       <c r="F93">
-        <v>1608</v>
+        <v>465</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483210</t>
+          <t xml:space="preserve">311475851</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-16</t>
+          <t xml:space="preserve">2030-11-16</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4681,25 +4681,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">9168077</t>
+          <t xml:space="preserve">9370842</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F94">
-        <v>885</v>
+        <v>784</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483220</t>
+          <t xml:space="preserve">311475844</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-16</t>
+          <t xml:space="preserve">2030-11-16</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4731,25 +4731,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">9168077</t>
+          <t xml:space="preserve">7010687</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F95">
-        <v>1356</v>
+        <v>722</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483216</t>
+          <t xml:space="preserve">311477758</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-16</t>
+          <t xml:space="preserve">2030-11-23</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2210082</t>
+          <t xml:space="preserve">5299224</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4790,16 +4790,16 @@
         </is>
       </c>
       <c r="F96">
-        <v>514</v>
+        <v>1608</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483562</t>
+          <t xml:space="preserve">311483210</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-17</t>
+          <t xml:space="preserve">2030-12-16</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4831,25 +4831,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">9168077</t>
+          <t xml:space="preserve">2210082</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F97">
-        <v>530</v>
+        <v>514</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483961</t>
+          <t xml:space="preserve">311483562</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-18</t>
+          <t xml:space="preserve">2030-12-17</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4881,25 +4881,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">9168077</t>
+          <t xml:space="preserve">2597534</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F98">
-        <v>1128</v>
+        <v>600</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483963</t>
+          <t xml:space="preserve">311483621</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-18</t>
+          <t xml:space="preserve">2030-12-17</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4931,25 +4931,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">10175791</t>
+          <t xml:space="preserve">2597534</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F99">
-        <v>354</v>
+        <v>948</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311484259</t>
+          <t xml:space="preserve">311483621</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-21</t>
+          <t xml:space="preserve">2030-12-17</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4981,25 +4981,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">10175791</t>
+          <t xml:space="preserve">9168077</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F100">
-        <v>428</v>
+        <v>885</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311484263</t>
+          <t xml:space="preserve">311483967</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-21</t>
+          <t xml:space="preserve">2030-12-18</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5031,25 +5031,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209985</t>
+          <t xml:space="preserve">9168077</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F101">
-        <v>1171</v>
+        <v>530</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311484281</t>
+          <t xml:space="preserve">311483961</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-21</t>
+          <t xml:space="preserve">2030-12-18</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5081,25 +5081,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2597534</t>
+          <t xml:space="preserve">9168077</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F102">
-        <v>437</v>
+        <v>1128</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311484253</t>
+          <t xml:space="preserve">311483963</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-21</t>
+          <t xml:space="preserve">2030-12-18</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5131,25 +5131,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2216228</t>
+          <t xml:space="preserve">9168077</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F103">
-        <v>504</v>
+        <v>1356</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311489560</t>
+          <t xml:space="preserve">311483967</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-22</t>
+          <t xml:space="preserve">2030-12-18</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">5300128</t>
+          <t xml:space="preserve">10175791</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -5190,16 +5190,16 @@
         </is>
       </c>
       <c r="F104">
-        <v>803</v>
+        <v>354</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311491356</t>
+          <t xml:space="preserve">311484259</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-29</t>
+          <t xml:space="preserve">2030-12-21</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5231,25 +5231,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">7562165</t>
+          <t xml:space="preserve">10175791</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F105">
-        <v>524</v>
+        <v>428</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311491358</t>
+          <t xml:space="preserve">311484263</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-29</t>
+          <t xml:space="preserve">2030-12-21</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2214316</t>
+          <t xml:space="preserve">2209985</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -5290,16 +5290,16 @@
         </is>
       </c>
       <c r="F106">
-        <v>266</v>
+        <v>1171</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311493260</t>
+          <t xml:space="preserve">311484281</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-05</t>
+          <t xml:space="preserve">2030-12-21</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5331,25 +5331,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2219479</t>
+          <t xml:space="preserve">2597534</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F107">
-        <v>689</v>
+        <v>437</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311493605</t>
+          <t xml:space="preserve">311484253</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-08</t>
+          <t xml:space="preserve">2030-12-21</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">100298242, 100298243</t>
+          <t xml:space="preserve">2216228</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -5390,16 +5390,16 @@
         </is>
       </c>
       <c r="F108">
-        <v>2442</v>
+        <v>504</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311500199</t>
+          <t xml:space="preserve">311489560</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-03</t>
+          <t xml:space="preserve">2031-01-22</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2595487</t>
+          <t xml:space="preserve">5300128</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -5440,16 +5440,16 @@
         </is>
       </c>
       <c r="F109">
-        <v>873</v>
+        <v>803</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311504181</t>
+          <t xml:space="preserve">311491356</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-17</t>
+          <t xml:space="preserve">2031-01-29</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5481,25 +5481,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2595646</t>
+          <t xml:space="preserve">7562165</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F110">
-        <v>1660</v>
+        <v>524</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311504185</t>
+          <t xml:space="preserve">311491358</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-17</t>
+          <t xml:space="preserve">2031-01-29</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5531,25 +5531,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2589978</t>
+          <t xml:space="preserve">2214316</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F111">
-        <v>580</v>
+        <v>266</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311510338</t>
+          <t xml:space="preserve">311493260</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-07</t>
+          <t xml:space="preserve">2031-02-05</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2591660</t>
+          <t xml:space="preserve">2219479</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -5590,16 +5590,16 @@
         </is>
       </c>
       <c r="F112">
-        <v>313</v>
+        <v>689</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311510335</t>
+          <t xml:space="preserve">311493605</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-07</t>
+          <t xml:space="preserve">2031-02-08</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5631,25 +5631,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">100039640</t>
+          <t xml:space="preserve">2595487</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F113">
-        <v>1189</v>
+        <v>873</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311512586</t>
+          <t xml:space="preserve">311504181</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-15</t>
+          <t xml:space="preserve">2031-03-17</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5681,25 +5681,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209908</t>
+          <t xml:space="preserve">2595646</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F114">
-        <v>422</v>
+        <v>1660</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311513456</t>
+          <t xml:space="preserve">311504185</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-19</t>
+          <t xml:space="preserve">2031-03-17</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5731,25 +5731,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2591270</t>
+          <t xml:space="preserve">2589978</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F115">
-        <v>380</v>
+        <v>580</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311513452</t>
+          <t xml:space="preserve">311510337</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-19</t>
+          <t xml:space="preserve">2031-04-07</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5781,25 +5781,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">5302628</t>
+          <t xml:space="preserve">2589978</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F116">
-        <v>453</v>
+        <v>252</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311513379</t>
+          <t xml:space="preserve">311510337</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-19</t>
+          <t xml:space="preserve">2031-04-07</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">8352544</t>
+          <t xml:space="preserve">2591660</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -5840,16 +5840,16 @@
         </is>
       </c>
       <c r="F117">
-        <v>485</v>
+        <v>313</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311513468</t>
+          <t xml:space="preserve">311510335</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-19</t>
+          <t xml:space="preserve">2031-04-07</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5881,25 +5881,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2594623</t>
+          <t xml:space="preserve">2209946</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F118">
-        <v>416</v>
+        <v>286</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311514520</t>
+          <t xml:space="preserve">311512262</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-22</t>
+          <t xml:space="preserve">2031-04-14</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5931,25 +5931,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2595960</t>
+          <t xml:space="preserve">100039640</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F119">
-        <v>1279</v>
+        <v>1189</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311517451</t>
+          <t xml:space="preserve">311512586</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-04</t>
+          <t xml:space="preserve">2031-04-15</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -5981,25 +5981,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940846</t>
+          <t xml:space="preserve">2209908</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F120">
-        <v>400</v>
+        <v>422</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311517474</t>
+          <t xml:space="preserve">311513456</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-04</t>
+          <t xml:space="preserve">2031-04-19</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">5301648</t>
+          <t xml:space="preserve">2591270</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -6040,16 +6040,16 @@
         </is>
       </c>
       <c r="F121">
-        <v>480</v>
+        <v>380</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311519301</t>
+          <t xml:space="preserve">311513452</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-11</t>
+          <t xml:space="preserve">2031-04-19</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">5302765</t>
+          <t xml:space="preserve">5302628</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6090,16 +6090,16 @@
         </is>
       </c>
       <c r="F122">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311519300</t>
+          <t xml:space="preserve">311513379</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-11</t>
+          <t xml:space="preserve">2031-04-19</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">7609591</t>
+          <t xml:space="preserve">8352544</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6140,16 +6140,16 @@
         </is>
       </c>
       <c r="F123">
-        <v>285</v>
+        <v>485</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311519591</t>
+          <t xml:space="preserve">311513468</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-11</t>
+          <t xml:space="preserve">2031-04-19</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">8038405</t>
+          <t xml:space="preserve">2594623</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -6190,16 +6190,16 @@
         </is>
       </c>
       <c r="F124">
-        <v>544</v>
+        <v>416</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311519303</t>
+          <t xml:space="preserve">311514520</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-11</t>
+          <t xml:space="preserve">2031-04-22</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">8239899</t>
+          <t xml:space="preserve">2595960</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -6240,16 +6240,16 @@
         </is>
       </c>
       <c r="F125">
-        <v>611</v>
+        <v>1279</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311519304</t>
+          <t xml:space="preserve">311517451</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-11</t>
+          <t xml:space="preserve">2031-05-04</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6281,25 +6281,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">265067, 265068</t>
+          <t xml:space="preserve">8940846</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F126">
-        <v>2578</v>
+        <v>400</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311519776</t>
+          <t xml:space="preserve">311517474</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-12</t>
+          <t xml:space="preserve">2031-05-04</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209991</t>
+          <t xml:space="preserve">5301648</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -6340,16 +6340,16 @@
         </is>
       </c>
       <c r="F127">
-        <v>520</v>
+        <v>480</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311521608</t>
+          <t xml:space="preserve">311519301</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-20</t>
+          <t xml:space="preserve">2031-05-11</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6381,25 +6381,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">5300240</t>
+          <t xml:space="preserve">5302765</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F128">
-        <v>1275</v>
+        <v>455</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311527885</t>
+          <t xml:space="preserve">311519300</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-14</t>
+          <t xml:space="preserve">2031-05-11</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2214307</t>
+          <t xml:space="preserve">7609591</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -6440,16 +6440,16 @@
         </is>
       </c>
       <c r="F129">
-        <v>2884</v>
+        <v>285</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533128</t>
+          <t xml:space="preserve">311519591</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-02</t>
+          <t xml:space="preserve">2031-05-11</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6481,25 +6481,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2214307</t>
+          <t xml:space="preserve">8038405</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F130">
-        <v>972</v>
+        <v>544</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533129</t>
+          <t xml:space="preserve">311519303</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-02</t>
+          <t xml:space="preserve">2031-05-11</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6531,25 +6531,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2593904</t>
+          <t xml:space="preserve">8239899</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F131">
-        <v>704</v>
+        <v>611</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533127</t>
+          <t xml:space="preserve">311519304</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-02</t>
+          <t xml:space="preserve">2031-05-11</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">268651</t>
+          <t xml:space="preserve">2209991</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -6590,16 +6590,16 @@
         </is>
       </c>
       <c r="F132">
-        <v>602</v>
+        <v>520</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533123</t>
+          <t xml:space="preserve">311521608</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-02</t>
+          <t xml:space="preserve">2031-05-20</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6631,25 +6631,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">268652, 268653</t>
+          <t xml:space="preserve">5300240</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F133">
-        <v>2677</v>
+        <v>1275</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533125</t>
+          <t xml:space="preserve">311527885</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-02</t>
+          <t xml:space="preserve">2031-06-14</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">5300077</t>
+          <t xml:space="preserve">2214307</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -6690,11 +6690,11 @@
         </is>
       </c>
       <c r="F134">
-        <v>2139</v>
+        <v>2884</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533130</t>
+          <t xml:space="preserve">311533128</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -6731,20 +6731,20 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">5300077</t>
+          <t xml:space="preserve">2214307</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F135">
-        <v>1158</v>
+        <v>972</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533130</t>
+          <t xml:space="preserve">311533129</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -6781,25 +6781,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2212560</t>
+          <t xml:space="preserve">2593904</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F136">
-        <v>403</v>
+        <v>704</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533516</t>
+          <t xml:space="preserve">311533127</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-05</t>
+          <t xml:space="preserve">2031-07-02</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2593898</t>
+          <t xml:space="preserve">5300077</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -6840,16 +6840,16 @@
         </is>
       </c>
       <c r="F137">
-        <v>5774</v>
+        <v>2139</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533502</t>
+          <t xml:space="preserve">311533130</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-05</t>
+          <t xml:space="preserve">2031-07-02</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6881,25 +6881,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2593898</t>
+          <t xml:space="preserve">5300077</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F138">
-        <v>544</v>
+        <v>1158</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533496</t>
+          <t xml:space="preserve">311533130</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-05</t>
+          <t xml:space="preserve">2031-07-02</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">7382834</t>
+          <t xml:space="preserve">2212560</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -6940,11 +6940,11 @@
         </is>
       </c>
       <c r="F139">
-        <v>1002</v>
+        <v>403</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533492</t>
+          <t xml:space="preserve">311533516</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">8127101</t>
+          <t xml:space="preserve">2593898</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -6990,11 +6990,11 @@
         </is>
       </c>
       <c r="F140">
-        <v>557</v>
+        <v>5774</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533512</t>
+          <t xml:space="preserve">311533502</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -7031,20 +7031,20 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">8314790</t>
+          <t xml:space="preserve">2593898</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F141">
-        <v>5811</v>
+        <v>544</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533528</t>
+          <t xml:space="preserve">311533496</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">8738812</t>
+          <t xml:space="preserve">7382834</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -7090,11 +7090,11 @@
         </is>
       </c>
       <c r="F142">
-        <v>511</v>
+        <v>1002</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533507</t>
+          <t xml:space="preserve">311533492</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2215752</t>
+          <t xml:space="preserve">8127101</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -7140,16 +7140,16 @@
         </is>
       </c>
       <c r="F143">
-        <v>2429</v>
+        <v>557</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311538964</t>
+          <t xml:space="preserve">311533512</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-04</t>
+          <t xml:space="preserve">2031-07-05</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2595280</t>
+          <t xml:space="preserve">8314790</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -7190,16 +7190,16 @@
         </is>
       </c>
       <c r="F144">
-        <v>996</v>
+        <v>5811</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311538975</t>
+          <t xml:space="preserve">311533528</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-04</t>
+          <t xml:space="preserve">2031-07-05</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">5301218</t>
+          <t xml:space="preserve">8738812</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -7240,16 +7240,16 @@
         </is>
       </c>
       <c r="F145">
-        <v>3420</v>
+        <v>511</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311538952</t>
+          <t xml:space="preserve">311533507</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-04</t>
+          <t xml:space="preserve">2031-07-05</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">8314762</t>
+          <t xml:space="preserve">2215752</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -7290,11 +7290,11 @@
         </is>
       </c>
       <c r="F146">
-        <v>1551</v>
+        <v>2429</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311538960</t>
+          <t xml:space="preserve">311538964</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -7331,20 +7331,20 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">8314762</t>
+          <t xml:space="preserve">2595280</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F147">
-        <v>4950</v>
+        <v>996</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311538960</t>
+          <t xml:space="preserve">311538975</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -7381,20 +7381,20 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">8314762</t>
+          <t xml:space="preserve">5301218</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F148">
-        <v>906</v>
+        <v>3420</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311538960</t>
+          <t xml:space="preserve">311538952</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2595904</t>
+          <t xml:space="preserve">8314762</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -7440,16 +7440,16 @@
         </is>
       </c>
       <c r="F149">
-        <v>7177</v>
+        <v>1551</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539441</t>
+          <t xml:space="preserve">311538960</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-06</t>
+          <t xml:space="preserve">2031-08-04</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -7481,25 +7481,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209661</t>
+          <t xml:space="preserve">8314762</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F150">
-        <v>2435</v>
+        <v>4950</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539909</t>
+          <t xml:space="preserve">311538960</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-10</t>
+          <t xml:space="preserve">2031-08-04</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -7531,25 +7531,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209661</t>
+          <t xml:space="preserve">8314762</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F151">
-        <v>720</v>
+        <v>906</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539909</t>
+          <t xml:space="preserve">311538960</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-10</t>
+          <t xml:space="preserve">2031-08-04</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -7581,25 +7581,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209661</t>
+          <t xml:space="preserve">2595904</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F152">
-        <v>1218</v>
+        <v>7177</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539909</t>
+          <t xml:space="preserve">311539435</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-10</t>
+          <t xml:space="preserve">2031-08-06</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -7631,25 +7631,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209661</t>
+          <t xml:space="preserve">2595904</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F153">
-        <v>1187</v>
+        <v>650</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539909</t>
+          <t xml:space="preserve">311539435</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-10</t>
+          <t xml:space="preserve">2031-08-06</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -7686,15 +7686,15 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F154">
-        <v>1590</v>
+        <v>2435</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539909</t>
+          <t xml:space="preserve">311539849</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -7736,15 +7736,15 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F155">
-        <v>3575</v>
+        <v>720</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539909</t>
+          <t xml:space="preserve">311539849</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -7781,25 +7781,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">8948780</t>
+          <t xml:space="preserve">2209661</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F156">
-        <v>253</v>
+        <v>1218</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540512</t>
+          <t xml:space="preserve">311539849</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-12</t>
+          <t xml:space="preserve">2031-08-10</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">8948780</t>
+          <t xml:space="preserve">2209661</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -7840,16 +7840,16 @@
         </is>
       </c>
       <c r="F157">
-        <v>980</v>
+        <v>1187</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540512</t>
+          <t xml:space="preserve">311539849</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-12</t>
+          <t xml:space="preserve">2031-08-10</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -7881,25 +7881,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2212648</t>
+          <t xml:space="preserve">2209661</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F158">
-        <v>443</v>
+        <v>1590</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540701</t>
+          <t xml:space="preserve">311539849</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-13</t>
+          <t xml:space="preserve">2031-08-10</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -7931,25 +7931,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">100040993</t>
+          <t xml:space="preserve">2209661</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F159">
-        <v>756</v>
+        <v>3575</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311543562</t>
+          <t xml:space="preserve">311539849</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-26</t>
+          <t xml:space="preserve">2031-08-10</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">5299406</t>
+          <t xml:space="preserve">8948780</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -7990,16 +7990,16 @@
         </is>
       </c>
       <c r="F160">
-        <v>481</v>
+        <v>253</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311544545</t>
+          <t xml:space="preserve">311540512</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-31</t>
+          <t xml:space="preserve">2031-08-12</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -8031,25 +8031,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940846</t>
+          <t xml:space="preserve">8948780</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F161">
-        <v>8394</v>
+        <v>980</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311544560</t>
+          <t xml:space="preserve">311540512</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-31</t>
+          <t xml:space="preserve">2031-08-12</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -8081,25 +8081,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2589978</t>
+          <t xml:space="preserve">2212648</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F162">
-        <v>390</v>
+        <v>443</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311545404</t>
+          <t xml:space="preserve">311540701</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-02</t>
+          <t xml:space="preserve">2031-08-13</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -8131,25 +8131,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2589978</t>
+          <t xml:space="preserve">100040993</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F163">
-        <v>390</v>
+        <v>756</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311545404</t>
+          <t xml:space="preserve">311543562</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-02</t>
+          <t xml:space="preserve">2031-08-26</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -8181,25 +8181,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2589978</t>
+          <t xml:space="preserve">5299406</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F164">
-        <v>254</v>
+        <v>481</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311545528</t>
+          <t xml:space="preserve">311544545</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-02</t>
+          <t xml:space="preserve">2031-08-31</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2590529</t>
+          <t xml:space="preserve">8940846</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -8240,16 +8240,16 @@
         </is>
       </c>
       <c r="F165">
-        <v>590</v>
+        <v>8394</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549276</t>
+          <t xml:space="preserve">311544560</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-20</t>
+          <t xml:space="preserve">2031-08-31</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -8281,25 +8281,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298617</t>
+          <t xml:space="preserve">2589978</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F166">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549360</t>
+          <t xml:space="preserve">311545404</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-20</t>
+          <t xml:space="preserve">2031-09-02</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -8331,25 +8331,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2214735</t>
+          <t xml:space="preserve">2589978</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F167">
-        <v>312</v>
+        <v>390</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311550074</t>
+          <t xml:space="preserve">311545404</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-22</t>
+          <t xml:space="preserve">2031-09-02</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -8381,25 +8381,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2214735</t>
+          <t xml:space="preserve">2589978</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F168">
-        <v>416</v>
+        <v>254</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311550074</t>
+          <t xml:space="preserve">311545528</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-22</t>
+          <t xml:space="preserve">2031-09-02</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">9223091</t>
+          <t xml:space="preserve">2590529</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -8440,16 +8440,16 @@
         </is>
       </c>
       <c r="F169">
-        <v>5045</v>
+        <v>590</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311550306</t>
+          <t xml:space="preserve">311549276</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-23</t>
+          <t xml:space="preserve">2031-09-20</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2589978</t>
+          <t xml:space="preserve">5298617</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -8490,16 +8490,16 @@
         </is>
       </c>
       <c r="F170">
-        <v>6715</v>
+        <v>386</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561871</t>
+          <t xml:space="preserve">311549360</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-15</t>
+          <t xml:space="preserve">2031-09-20</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -8531,25 +8531,25 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2589978</t>
+          <t xml:space="preserve">2214735</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F171">
-        <v>2017</v>
+        <v>312</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561871</t>
+          <t xml:space="preserve">311550074</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-15</t>
+          <t xml:space="preserve">2031-09-22</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -8581,25 +8581,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2589978</t>
+          <t xml:space="preserve">2214735</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F172">
-        <v>1359</v>
+        <v>416</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561871</t>
+          <t xml:space="preserve">311550074</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-15</t>
+          <t xml:space="preserve">2031-09-22</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">100013861</t>
+          <t xml:space="preserve">9223091</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -8640,16 +8640,16 @@
         </is>
       </c>
       <c r="F173">
-        <v>3292</v>
+        <v>5045</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566593</t>
+          <t xml:space="preserve">311550306</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-07</t>
+          <t xml:space="preserve">2031-09-23</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -8681,25 +8681,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2215842</t>
+          <t xml:space="preserve">2589978</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F174">
-        <v>676</v>
+        <v>6715</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568002</t>
+          <t xml:space="preserve">311561871</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-15</t>
+          <t xml:space="preserve">2031-11-15</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -8731,25 +8731,25 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">266956, 266957</t>
+          <t xml:space="preserve">2589978</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F175">
-        <v>7502</v>
+        <v>2017</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311570444</t>
+          <t xml:space="preserve">311561871</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-04</t>
+          <t xml:space="preserve">2031-11-15</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -8781,25 +8781,25 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">266956, 266958</t>
+          <t xml:space="preserve">2589978</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F176">
-        <v>4799</v>
+        <v>1359</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311570444</t>
+          <t xml:space="preserve">311561871</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-04</t>
+          <t xml:space="preserve">2031-11-15</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">9492257</t>
+          <t xml:space="preserve">100013861</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -8840,16 +8840,16 @@
         </is>
       </c>
       <c r="F177">
-        <v>856</v>
+        <v>3292</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571109</t>
+          <t xml:space="preserve">311566593</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-07</t>
+          <t xml:space="preserve">2031-12-07</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">8314862</t>
+          <t xml:space="preserve">2215842</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -8890,16 +8890,16 @@
         </is>
       </c>
       <c r="F178">
-        <v>4490</v>
+        <v>676</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311574331</t>
+          <t xml:space="preserve">311568002</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-25</t>
+          <t xml:space="preserve">2031-12-15</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">5301791</t>
+          <t xml:space="preserve">9492257</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -8940,16 +8940,16 @@
         </is>
       </c>
       <c r="F179">
-        <v>5745</v>
+        <v>856</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311574812</t>
+          <t xml:space="preserve">311571109</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-26</t>
+          <t xml:space="preserve">2032-01-07</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -8981,25 +8981,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">5301791</t>
+          <t xml:space="preserve">8314862</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F180">
-        <v>1353</v>
+        <v>4490</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311574812</t>
+          <t xml:space="preserve">311574331</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-26</t>
+          <t xml:space="preserve">2032-01-25</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">100041898</t>
+          <t xml:space="preserve">5301791</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -9040,16 +9040,16 @@
         </is>
       </c>
       <c r="F181">
-        <v>2276</v>
+        <v>5745</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311575628</t>
+          <t xml:space="preserve">311574812</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-31</t>
+          <t xml:space="preserve">2032-01-26</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -9081,25 +9081,25 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2219385</t>
+          <t xml:space="preserve">5301791</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F182">
-        <v>1776</v>
+        <v>1353</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311578008</t>
+          <t xml:space="preserve">311574812</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-10</t>
+          <t xml:space="preserve">2032-01-26</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -9131,25 +9131,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2219385</t>
+          <t xml:space="preserve">100041898</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F183">
-        <v>701</v>
+        <v>2276</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311578008</t>
+          <t xml:space="preserve">311575628</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-10</t>
+          <t xml:space="preserve">2032-01-31</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -9186,11 +9186,11 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F184">
-        <v>1695</v>
+        <v>1776</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
@@ -9236,11 +9236,11 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F185">
-        <v>933</v>
+        <v>701</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
@@ -9286,11 +9286,11 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F186">
-        <v>966</v>
+        <v>1695</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
@@ -9336,11 +9336,11 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F187">
-        <v>1139</v>
+        <v>933</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
@@ -9386,11 +9386,11 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F188">
-        <v>846</v>
+        <v>966</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
@@ -9431,25 +9431,25 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940960</t>
+          <t xml:space="preserve">2219385</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F189">
-        <v>4713</v>
+        <v>1139</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582210</t>
+          <t xml:space="preserve">311578008</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-03</t>
+          <t xml:space="preserve">2032-02-10</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -9481,25 +9481,25 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940960</t>
+          <t xml:space="preserve">2219385</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F190">
-        <v>629</v>
+        <v>846</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582210</t>
+          <t xml:space="preserve">311578008</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-03</t>
+          <t xml:space="preserve">2032-02-10</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -9531,25 +9531,25 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298857</t>
+          <t xml:space="preserve">8940960</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F191">
-        <v>972</v>
+        <v>4713</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311583248</t>
+          <t xml:space="preserve">311582210</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-08</t>
+          <t xml:space="preserve">2032-03-03</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -9581,25 +9581,25 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298849</t>
+          <t xml:space="preserve">8940960</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F192">
-        <v>876</v>
+        <v>629</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311583573</t>
+          <t xml:space="preserve">311582210</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-09</t>
+          <t xml:space="preserve">2032-03-03</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -9631,25 +9631,25 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298858</t>
+          <t xml:space="preserve">5298857</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F193">
-        <v>1657</v>
+        <v>972</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311583564</t>
+          <t xml:space="preserve">311583248</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-09</t>
+          <t xml:space="preserve">2032-03-08</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -9681,7 +9681,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298858</t>
+          <t xml:space="preserve">5298849</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -9690,11 +9690,11 @@
         </is>
       </c>
       <c r="F194">
-        <v>1651</v>
+        <v>876</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311583564</t>
+          <t xml:space="preserve">311583573</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -9731,25 +9731,25 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t xml:space="preserve">268650, 268651</t>
+          <t xml:space="preserve">5298858</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F195">
-        <v>1122</v>
+        <v>1657</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311584438</t>
+          <t xml:space="preserve">311583564</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-11</t>
+          <t xml:space="preserve">2032-03-09</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -9781,25 +9781,25 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298996</t>
+          <t xml:space="preserve">5298858</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F196">
-        <v>499</v>
+        <v>1651</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311584350</t>
+          <t xml:space="preserve">311583564</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-11</t>
+          <t xml:space="preserve">2032-03-09</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -9836,11 +9836,11 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F197">
-        <v>347</v>
+        <v>499</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -9886,11 +9886,11 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F198">
-        <v>800</v>
+        <v>347</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
@@ -9931,25 +9931,25 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t xml:space="preserve">8195911</t>
+          <t xml:space="preserve">5298996</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F199">
-        <v>292</v>
+        <v>800</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586697</t>
+          <t xml:space="preserve">311584350</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-21</t>
+          <t xml:space="preserve">2032-03-11</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -9981,25 +9981,25 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t xml:space="preserve">265103</t>
+          <t xml:space="preserve">8195911</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F200">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311597207</t>
+          <t xml:space="preserve">311586697</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-03</t>
+          <t xml:space="preserve">2032-03-21</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -10131,7 +10131,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t xml:space="preserve">5299445</t>
+          <t xml:space="preserve">100090478</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -10140,16 +10140,16 @@
         </is>
       </c>
       <c r="F203">
-        <v>1589</v>
+        <v>2788</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311637067</t>
+          <t xml:space="preserve">311626787</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-20</t>
+          <t xml:space="preserve">2032-09-09</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2219342</t>
+          <t xml:space="preserve">5299445</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -10190,16 +10190,16 @@
         </is>
       </c>
       <c r="F204">
-        <v>1190</v>
+        <v>1589</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719130</t>
+          <t xml:space="preserve">311637067</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-01</t>
+          <t xml:space="preserve">2032-10-20</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t xml:space="preserve">8960384</t>
+          <t xml:space="preserve">2219342</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -10240,16 +10240,16 @@
         </is>
       </c>
       <c r="F205">
-        <v>1820</v>
+        <v>1190</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311724352</t>
+          <t xml:space="preserve">311719130</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-23</t>
+          <t xml:space="preserve">2033-11-01</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -10281,25 +10281,25 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve">271380, 271381</t>
+          <t xml:space="preserve">8960384</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F206">
-        <v>1104</v>
+        <v>1820</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725609</t>
+          <t xml:space="preserve">311724352</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-29</t>
+          <t xml:space="preserve">2033-11-23</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">

--- a/public/exports/29189374.xlsx
+++ b/public/exports/29189374.xlsx
@@ -91,26 +91,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 120</t>
+          <t xml:space="preserve">Billesborgvej 42A</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4681</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100165388</t>
+          <t xml:space="preserve">8314761, 100794736</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H2">
-        <v>1896</v>
+        <v>262</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,17 +151,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indian Kaj 4</t>
+          <t xml:space="preserve">Buen 5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4623</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100242692, 100939604</t>
+          <t xml:space="preserve">8314669</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -170,7 +170,7 @@
         </is>
       </c>
       <c r="H3">
-        <v>2403</v>
+        <v>259</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,26 +211,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Stadion 6</t>
+          <t xml:space="preserve">Buen 5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4623</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">100298242, 100298243</t>
+          <t xml:space="preserve">8314669</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H4">
-        <v>2442</v>
+        <v>259</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,26 +271,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglebæk Alle 3A</t>
+          <t xml:space="preserve">Byvej 33</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4682</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">100447736</t>
+          <t xml:space="preserve">2597454</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H5">
-        <v>974</v>
+        <v>443</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,7 +331,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnsborgvej 3B</t>
+          <t xml:space="preserve">Bådehavnen 14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -341,16 +341,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">100450727</t>
+          <t xml:space="preserve">718839, 5300196</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H6">
-        <v>1399</v>
+        <v>300</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,26 +391,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tornbjergvej 42</t>
+          <t xml:space="preserve">Bådehavnen 19</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">4623</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2211891</t>
+          <t xml:space="preserve">718843, 5300201</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="H7">
-        <v>583</v>
+        <v>400</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,7 +451,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngvej 12B</t>
+          <t xml:space="preserve">Bådehavnen 21</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -461,16 +461,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2215474</t>
+          <t xml:space="preserve">718836, 5300194</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H8">
-        <v>311</v>
+        <v>467</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -511,7 +511,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngtoften 24</t>
+          <t xml:space="preserve">Bådehavnen 6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -521,16 +521,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2215682</t>
+          <t xml:space="preserve">718840, 5300198</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H9">
-        <v>490</v>
+        <v>300</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngtoften 38</t>
+          <t xml:space="preserve">Fuglebæk Alle 3A</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -581,16 +581,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2215682</t>
+          <t xml:space="preserve">100447736</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H10">
-        <v>252</v>
+        <v>974</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tigervej 20</t>
+          <t xml:space="preserve">Gymnasievej 28</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -641,16 +641,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2216228</t>
+          <t xml:space="preserve">5301893</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H11">
-        <v>259</v>
+        <v>808</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tigervej 20</t>
+          <t xml:space="preserve">Gymnasievej 30A</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -701,16 +701,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2216228</t>
+          <t xml:space="preserve">5301893</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H12">
-        <v>259</v>
+        <v>918</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ølsemagle Kirkevej 60</t>
+          <t xml:space="preserve">Gymnasievej 30B</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2220022</t>
+          <t xml:space="preserve">5301893</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="H13">
-        <v>299</v>
+        <v>981</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -811,26 +811,26 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 33</t>
+          <t xml:space="preserve">Gymnasievej 30D</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">4682</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2597454</t>
+          <t xml:space="preserve">5301893</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H14">
-        <v>443</v>
+        <v>816</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -871,17 +871,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 65</t>
+          <t xml:space="preserve">Indian Kaj 4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">4140</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">265067, 265068</t>
+          <t xml:space="preserve">100242692, 100939604</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="H15">
-        <v>2578</v>
+        <v>2403</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Stadion 10</t>
+          <t xml:space="preserve">Lyngtoften 24</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">265103</t>
+          <t xml:space="preserve">2215682</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="H16">
-        <v>298</v>
+        <v>490</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvet 1</t>
+          <t xml:space="preserve">Lyngtoften 38</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1001,16 +1001,16 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">266956, 266957</t>
+          <t xml:space="preserve">2215682</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H17">
-        <v>7502</v>
+        <v>252</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvet 1</t>
+          <t xml:space="preserve">Lyngvej 12B</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1061,16 +1061,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">266956, 266958</t>
+          <t xml:space="preserve">2215474</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H18">
-        <v>4799</v>
+        <v>311</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerbæk Torv 30</t>
+          <t xml:space="preserve">Norsvej 2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1121,16 +1121,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">268650, 268651</t>
+          <t xml:space="preserve">8765343</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H19">
-        <v>1122</v>
+        <v>2988</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerbæk Torv 12</t>
+          <t xml:space="preserve">Norsvej 2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1181,16 +1181,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">268651</t>
+          <t xml:space="preserve">8765343</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H20">
-        <v>602</v>
+        <v>2512</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerbæk Torv 2</t>
+          <t xml:space="preserve">Norsvej 2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">268652, 268653</t>
+          <t xml:space="preserve">8765343</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1250,7 +1250,7 @@
         </is>
       </c>
       <c r="H21">
-        <v>2677</v>
+        <v>1540</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ølbycenter 64</t>
+          <t xml:space="preserve">Norsvej 2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1301,16 +1301,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">269957, 269958</t>
+          <t xml:space="preserve">8765343</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H22">
-        <v>2042</v>
+        <v>2844</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1351,26 +1351,26 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjæverskovhusene 34</t>
+          <t xml:space="preserve">Norsvej 2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">4632</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">271380, 271381</t>
+          <t xml:space="preserve">8765343</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H23">
-        <v>1104</v>
+        <v>1874</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sygehusvej 25</t>
+          <t xml:space="preserve">Norsvej 6</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1421,16 +1421,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298996</t>
+          <t xml:space="preserve">8769222</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H24">
-        <v>1261</v>
+        <v>987</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sygehusvej 25A</t>
+          <t xml:space="preserve">Nørre Boulevard 107</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1481,16 +1481,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298996</t>
+          <t xml:space="preserve">5300078</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H25">
-        <v>2331</v>
+        <v>1287</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sygehusvej 25</t>
+          <t xml:space="preserve">Overdrevsvejen 26</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1541,16 +1541,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298996</t>
+          <t xml:space="preserve">5302896</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H26">
-        <v>346</v>
+        <v>395</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørre Boulevard 107</t>
+          <t xml:space="preserve">Parkvej 120</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1601,16 +1601,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5300078</t>
+          <t xml:space="preserve">100165388</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H27">
-        <v>1287</v>
+        <v>1896</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ølbyvej 50</t>
+          <t xml:space="preserve">Ravnsborgvej 1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1661,16 +1661,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5301218</t>
+          <t xml:space="preserve">718828, 2594249</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H28">
-        <v>891</v>
+        <v>1067</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Alle 6</t>
+          <t xml:space="preserve">Ravnsborgvej 3A</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1721,16 +1721,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">5301281</t>
+          <t xml:space="preserve">718738, 2594250</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H29">
-        <v>577</v>
+        <v>1898</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Alle 6</t>
+          <t xml:space="preserve">Ravnsborgvej 3B</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1781,16 +1781,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">5301281</t>
+          <t xml:space="preserve">100450727</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="H30">
-        <v>340</v>
+        <v>1399</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gymnasievej 30B</t>
+          <t xml:space="preserve">Sygehusvej 25</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1841,16 +1841,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">5301893</t>
+          <t xml:space="preserve">5298996</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H31">
-        <v>981</v>
+        <v>1261</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gymnasievej 30D</t>
+          <t xml:space="preserve">Sygehusvej 25</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1901,16 +1901,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">5301893</t>
+          <t xml:space="preserve">5298996</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H32">
-        <v>816</v>
+        <v>346</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gymnasievej 30A</t>
+          <t xml:space="preserve">Sygehusvej 25A</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1961,16 +1961,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">5301893</t>
+          <t xml:space="preserve">5298996</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H33">
-        <v>918</v>
+        <v>2331</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gymnasievej 28</t>
+          <t xml:space="preserve">Søbækvej 1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2021,16 +2021,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">5301893</t>
+          <t xml:space="preserve">7781206</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H34">
-        <v>808</v>
+        <v>1240</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overdrevsvejen 26</t>
+          <t xml:space="preserve">Søndre Alle 6</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2081,16 +2081,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">5302896</t>
+          <t xml:space="preserve">5301281</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H35">
-        <v>395</v>
+        <v>577</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnsborgvej 3A</t>
+          <t xml:space="preserve">Søndre Alle 6</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2141,16 +2141,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">718738, 2594250</t>
+          <t xml:space="preserve">5301281</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H36">
-        <v>1898</v>
+        <v>340</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnsborgvej 1</t>
+          <t xml:space="preserve">Tigervej 20</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2201,16 +2201,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">718828, 2594249</t>
+          <t xml:space="preserve">2216228</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H37">
-        <v>1067</v>
+        <v>259</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bådehavnen 21</t>
+          <t xml:space="preserve">Tigervej 20</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2261,16 +2261,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">718836, 5300194</t>
+          <t xml:space="preserve">2216228</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H38">
-        <v>467</v>
+        <v>259</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2311,26 +2311,26 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bådehavnen 14</t>
+          <t xml:space="preserve">Tornbjergvej 42</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4623</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">718839, 5300196</t>
+          <t xml:space="preserve">2211891</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H39">
-        <v>300</v>
+        <v>583</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bådehavnen 6</t>
+          <t xml:space="preserve">Ved Stadion 4</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2381,16 +2381,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">718840, 5300198</t>
+          <t xml:space="preserve">8314857</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H40">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bådehavnen 19</t>
+          <t xml:space="preserve">Ved Stadion 4</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2441,16 +2441,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">718843, 5300201</t>
+          <t xml:space="preserve">8314857</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H41">
-        <v>400</v>
+        <v>1222</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søbækvej 1</t>
+          <t xml:space="preserve">Ved Stadion 4</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2501,16 +2501,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">7781206</t>
+          <t xml:space="preserve">8314857</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H42">
-        <v>1240</v>
+        <v>271</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2551,26 +2551,26 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buen 5</t>
+          <t xml:space="preserve">Vindegårdsvej 1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">4623</t>
+          <t xml:space="preserve">4632</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">8314669</t>
+          <t xml:space="preserve">8940960</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H43">
-        <v>259</v>
+        <v>305</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2611,26 +2611,26 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buen 5</t>
+          <t xml:space="preserve">Vindegårdsvej 1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">4623</t>
+          <t xml:space="preserve">4632</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">8314669</t>
+          <t xml:space="preserve">8940960</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H44">
-        <v>259</v>
+        <v>595</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2671,26 +2671,26 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ølsemagle Kirkevej 62A</t>
+          <t xml:space="preserve">Vindegårdsvej 1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4632</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">8314712</t>
+          <t xml:space="preserve">8940960</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H45">
-        <v>285</v>
+        <v>637</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2731,26 +2731,26 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billesborgvej 42A</t>
+          <t xml:space="preserve">Vindegårdsvej 1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">4681</t>
+          <t xml:space="preserve">4632</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">8314761, 100794736</t>
+          <t xml:space="preserve">8940960</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H46">
-        <v>262</v>
+        <v>699</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Stadion 4</t>
+          <t xml:space="preserve">Ølbyvej 50</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2801,16 +2801,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">8314857</t>
+          <t xml:space="preserve">5301218</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H47">
-        <v>387</v>
+        <v>891</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Stadion 4</t>
+          <t xml:space="preserve">Ølsemagle Kirkevej 60</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2861,16 +2861,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">8314857</t>
+          <t xml:space="preserve">2220022</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H48">
-        <v>1222</v>
+        <v>299</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Stadion 4</t>
+          <t xml:space="preserve">Ølsemagle Kirkevej 62A</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2921,16 +2921,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">8314857</t>
+          <t xml:space="preserve">8314712</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H49">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norsvej 2</t>
+          <t xml:space="preserve">Bådehavnen 8</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2981,30 +2981,30 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">8765343</t>
+          <t xml:space="preserve">718862, 5300213</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H50">
-        <v>2988</v>
+        <v>300</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200000890</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2014-04-22</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3031,40 +3031,40 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norsvej 2</t>
+          <t xml:space="preserve">Højelsevej 1B</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4623</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">8765343</t>
+          <t xml:space="preserve">718875, 2214316</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H51">
-        <v>2512</v>
+        <v>2158</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">310015406</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2022-11-29</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norsvej 2</t>
+          <t xml:space="preserve">Ravnsborgvej 3</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3101,30 +3101,30 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">8765343</t>
+          <t xml:space="preserve">718829, 2594250</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H52">
-        <v>1540</v>
+        <v>3072</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">310023399</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-02-04</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3151,40 +3151,40 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norsvej 2</t>
+          <t xml:space="preserve">Vordingborgvej 124D</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4681</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">8765343</t>
+          <t xml:space="preserve">718877, 2595511</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H53">
-        <v>2844</v>
+        <v>3030</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">310023400</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-02-04</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norsvej 2</t>
+          <t xml:space="preserve">Ølbycenter 64</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3221,30 +3221,30 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">8765343</t>
+          <t xml:space="preserve">269957, 269958</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H54">
-        <v>1874</v>
+        <v>2042</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311067567</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2024-08-08</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norsvej 6</t>
+          <t xml:space="preserve">Ølbycenter 77B</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">8769222</t>
+          <t xml:space="preserve">9517472</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3290,21 +3290,21 @@
         </is>
       </c>
       <c r="H55">
-        <v>987</v>
+        <v>3416</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311067575</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2024-08-08</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3331,40 +3331,40 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vindegårdsvej 1</t>
+          <t xml:space="preserve">Ølbycenter 86</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">4632</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940960</t>
+          <t xml:space="preserve">9517473</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H56">
-        <v>305</v>
+        <v>3416</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311067568</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2024-08-08</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3391,40 +3391,40 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vindegårdsvej 1</t>
+          <t xml:space="preserve">Slimmingevej 94</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">4632</t>
+          <t xml:space="preserve">4100</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940960</t>
+          <t xml:space="preserve">2592022</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H57">
-        <v>595</v>
+        <v>699</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311165257</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-03-17</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3451,40 +3451,40 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vindegårdsvej 1</t>
+          <t xml:space="preserve">Slimmingevej 94</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">4632</t>
+          <t xml:space="preserve">4100</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940960</t>
+          <t xml:space="preserve">2592022</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H58">
-        <v>637</v>
+        <v>264</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311165256</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-03-17</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -3511,45 +3511,45 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vindegårdsvej 1</t>
+          <t xml:space="preserve">Bådehavnen 7A</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">4632</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940960</t>
+          <t xml:space="preserve">718841, 5300199</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="H59">
-        <v>699</v>
+        <v>393</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311228167</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2027-02-13</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bådehavnen 8</t>
+          <t xml:space="preserve">Baneledet 1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3581,35 +3581,35 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">718862, 5300213</t>
+          <t xml:space="preserve">5302948</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H60">
-        <v>300</v>
+        <v>642</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">200000890</t>
+          <t xml:space="preserve">311408662</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2014-04-22</t>
+          <t xml:space="preserve">2029-11-13</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3631,45 +3631,45 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højelsevej 1B</t>
+          <t xml:space="preserve">Havebo 2</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">4623</t>
+          <t xml:space="preserve">4681</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">718875, 2214316</t>
+          <t xml:space="preserve">2596007</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H61">
-        <v>2158</v>
+        <v>252</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">310015406</t>
+          <t xml:space="preserve">311461664</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-11-29</t>
+          <t xml:space="preserve">2030-09-17</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3691,45 +3691,45 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnsborgvej 3</t>
+          <t xml:space="preserve">Lundegårdsvej 2</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4100</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">718829, 2594250</t>
+          <t xml:space="preserve">2591592</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H62">
-        <v>3072</v>
+        <v>1453</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">310023399</t>
+          <t xml:space="preserve">311461620</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-02-04</t>
+          <t xml:space="preserve">2030-09-17</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3751,45 +3751,45 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vordingborgvej 124D</t>
+          <t xml:space="preserve">Lundegårdsvej 2</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">4681</t>
+          <t xml:space="preserve">4100</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">718877, 2595511</t>
+          <t xml:space="preserve">2591592</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H63">
-        <v>3030</v>
+        <v>628</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">310023400</t>
+          <t xml:space="preserve">311461620</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-02-04</t>
+          <t xml:space="preserve">2030-09-17</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3811,7 +3811,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ølbycenter 77B</t>
+          <t xml:space="preserve">Pedersvej 100</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">9517472</t>
+          <t xml:space="preserve">5299989</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3830,26 +3830,26 @@
         </is>
       </c>
       <c r="H64">
-        <v>3416</v>
+        <v>1278</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311067575</t>
+          <t xml:space="preserve">311461719</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-08-08</t>
+          <t xml:space="preserve">2030-09-17</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3871,45 +3871,45 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ølbycenter 86</t>
+          <t xml:space="preserve">Ejbovej 2</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4632</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">9517473</t>
+          <t xml:space="preserve">100000634</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H65">
-        <v>3416</v>
+        <v>840</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311067568</t>
+          <t xml:space="preserve">311461926</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-08-08</t>
+          <t xml:space="preserve">2030-09-18</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3931,17 +3931,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slimmingevej 94</t>
+          <t xml:space="preserve">Rishøjvej 1B</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">4100</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2592022</t>
+          <t xml:space="preserve">2219478</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3950,26 +3950,26 @@
         </is>
       </c>
       <c r="H66">
-        <v>699</v>
+        <v>383</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311165256</t>
+          <t xml:space="preserve">311461925</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-17</t>
+          <t xml:space="preserve">2030-09-18</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3991,45 +3991,45 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slimmingevej 94</t>
+          <t xml:space="preserve">Rishøjvej 3</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">4100</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2592022</t>
+          <t xml:space="preserve">2219384</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H67">
-        <v>264</v>
+        <v>367</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311165256</t>
+          <t xml:space="preserve">311462237</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-17</t>
+          <t xml:space="preserve">2030-09-21</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -4051,35 +4051,35 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bådehavnen 7A</t>
+          <t xml:space="preserve">Pogebanken 3</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4681</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">718841, 5300199</t>
+          <t xml:space="preserve">2595275</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H68">
-        <v>393</v>
+        <v>470</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311228167</t>
+          <t xml:space="preserve">311466054</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-13</t>
+          <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baneledet 1</t>
+          <t xml:space="preserve">Sankt Gertrudsstræde 30</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4121,25 +4121,25 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">5302948</t>
+          <t xml:space="preserve">5298693</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H69">
-        <v>642</v>
+        <v>325</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311408662</t>
+          <t xml:space="preserve">311468126</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-13</t>
+          <t xml:space="preserve">2030-10-20</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4171,17 +4171,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundegårdsvej 2</t>
+          <t xml:space="preserve">Pogebanken 7</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">4100</t>
+          <t xml:space="preserve">4681</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2591592</t>
+          <t xml:space="preserve">2595274</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4190,16 +4190,16 @@
         </is>
       </c>
       <c r="H70">
-        <v>1453</v>
+        <v>379</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311461620</t>
+          <t xml:space="preserve">311469400</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-17</t>
+          <t xml:space="preserve">2030-10-23</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4231,35 +4231,35 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundegårdsvej 2</t>
+          <t xml:space="preserve">Tangmosevej 1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">4100</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2591592</t>
+          <t xml:space="preserve">5299172</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H71">
-        <v>628</v>
+        <v>877</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311461620</t>
+          <t xml:space="preserve">311469402</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-17</t>
+          <t xml:space="preserve">2030-10-23</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4291,35 +4291,35 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havebo 2</t>
+          <t xml:space="preserve">Tangmosevej 1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">4681</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2596007</t>
+          <t xml:space="preserve">5299172</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H72">
-        <v>252</v>
+        <v>282</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311461664</t>
+          <t xml:space="preserve">311469399</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-17</t>
+          <t xml:space="preserve">2030-10-23</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pedersvej 100</t>
+          <t xml:space="preserve">Pogebanken 5</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4681</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">5299989</t>
+          <t xml:space="preserve">2595275</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4370,16 +4370,16 @@
         </is>
       </c>
       <c r="H73">
-        <v>1278</v>
+        <v>503</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311461719</t>
+          <t xml:space="preserve">311474129</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-17</t>
+          <t xml:space="preserve">2030-11-09</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4411,35 +4411,35 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejbovej 2</t>
+          <t xml:space="preserve">Boholtevej 181</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">4632</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">100000634</t>
+          <t xml:space="preserve">5302760</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H74">
-        <v>840</v>
+        <v>597</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311461926</t>
+          <t xml:space="preserve">311474331</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-18</t>
+          <t xml:space="preserve">2030-11-10</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rishøjvej 1B</t>
+          <t xml:space="preserve">Boholtevej 91</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2219478</t>
+          <t xml:space="preserve">5302764</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4490,16 +4490,16 @@
         </is>
       </c>
       <c r="H75">
-        <v>383</v>
+        <v>1199</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311461925</t>
+          <t xml:space="preserve">311474762</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-18</t>
+          <t xml:space="preserve">2030-11-11</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rishøjvej 3</t>
+          <t xml:space="preserve">Accisevej 1</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2219384</t>
+          <t xml:space="preserve">5299241</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4550,16 +4550,16 @@
         </is>
       </c>
       <c r="H76">
-        <v>367</v>
+        <v>734</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311462237</t>
+          <t xml:space="preserve">311475433</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-21</t>
+          <t xml:space="preserve">2030-11-13</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4591,35 +4591,35 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pogebanken 3</t>
+          <t xml:space="preserve">Allegade 3</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">4681</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2595275</t>
+          <t xml:space="preserve">5298850</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H77">
-        <v>470</v>
+        <v>321</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466054</t>
+          <t xml:space="preserve">311475476</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-08</t>
+          <t xml:space="preserve">2030-11-13</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sankt Gertrudsstræde 30</t>
+          <t xml:space="preserve">Boholtevej 85A</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298693</t>
+          <t xml:space="preserve">5302763</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4670,16 +4670,16 @@
         </is>
       </c>
       <c r="H78">
-        <v>325</v>
+        <v>1324</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311468126</t>
+          <t xml:space="preserve">311475438</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-20</t>
+          <t xml:space="preserve">2030-11-13</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4711,17 +4711,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pogebanken 7</t>
+          <t xml:space="preserve">Dyrlundsvej 11</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">4681</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2595274</t>
+          <t xml:space="preserve">5299044</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4730,16 +4730,16 @@
         </is>
       </c>
       <c r="H79">
-        <v>379</v>
+        <v>557</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311469400</t>
+          <t xml:space="preserve">311475426</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-23</t>
+          <t xml:space="preserve">2030-11-13</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tangmosevej 1</t>
+          <t xml:space="preserve">Karlemosevej 46</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">5299172</t>
+          <t xml:space="preserve">2215847</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4790,16 +4790,16 @@
         </is>
       </c>
       <c r="H80">
-        <v>877</v>
+        <v>552</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311469402</t>
+          <t xml:space="preserve">311475459</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-23</t>
+          <t xml:space="preserve">2030-11-13</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tangmosevej 1</t>
+          <t xml:space="preserve">Lerbæk Torv 5</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4841,25 +4841,25 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">5299172</t>
+          <t xml:space="preserve">2593903</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H81">
-        <v>282</v>
+        <v>722</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311469399</t>
+          <t xml:space="preserve">311475469</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-23</t>
+          <t xml:space="preserve">2030-11-13</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pogebanken 5</t>
+          <t xml:space="preserve">Østertorp 67</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2595275</t>
+          <t xml:space="preserve">2594914</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4910,16 +4910,16 @@
         </is>
       </c>
       <c r="H82">
-        <v>503</v>
+        <v>442</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474129</t>
+          <t xml:space="preserve">311475465</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-09</t>
+          <t xml:space="preserve">2030-11-13</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -4951,35 +4951,35 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boholtevej 181</t>
+          <t xml:space="preserve">Østertorp 68</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4681</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">5302760</t>
+          <t xml:space="preserve">2594914</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H83">
-        <v>597</v>
+        <v>502</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474331</t>
+          <t xml:space="preserve">311475465</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-10</t>
+          <t xml:space="preserve">2030-11-13</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boholtevej 91</t>
+          <t xml:space="preserve">Gymnasievej 22</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">5302764</t>
+          <t xml:space="preserve">8638680</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="H84">
-        <v>1199</v>
+        <v>465</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474762</t>
+          <t xml:space="preserve">311475851</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-11</t>
+          <t xml:space="preserve">2030-11-16</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karlemosevej 46</t>
+          <t xml:space="preserve">Gymnasievej 24</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2215847</t>
+          <t xml:space="preserve">9370842</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5090,16 +5090,16 @@
         </is>
       </c>
       <c r="H85">
-        <v>552</v>
+        <v>784</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475459</t>
+          <t xml:space="preserve">311475844</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-13</t>
+          <t xml:space="preserve">2030-11-16</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5131,17 +5131,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerbæk Torv 5</t>
+          <t xml:space="preserve">Mellemmarksvej 13</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4681</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2593903</t>
+          <t xml:space="preserve">7010687</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475469</t>
+          <t xml:space="preserve">311477758</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-13</t>
+          <t xml:space="preserve">2030-11-23</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5191,17 +5191,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østertorp 67</t>
+          <t xml:space="preserve">Slagterivej 12</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">4681</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2594914</t>
+          <t xml:space="preserve">5299224</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5210,16 +5210,16 @@
         </is>
       </c>
       <c r="H87">
-        <v>442</v>
+        <v>1608</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475465</t>
+          <t xml:space="preserve">311483210</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-13</t>
+          <t xml:space="preserve">2030-12-16</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5251,35 +5251,35 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østertorp 68</t>
+          <t xml:space="preserve">Byvej 31</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">4681</t>
+          <t xml:space="preserve">4682</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2594914</t>
+          <t xml:space="preserve">2597534</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H88">
-        <v>502</v>
+        <v>600</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475465</t>
+          <t xml:space="preserve">311483621</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-13</t>
+          <t xml:space="preserve">2030-12-17</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5311,35 +5311,35 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allegade 3</t>
+          <t xml:space="preserve">Byvej 31</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4682</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298850</t>
+          <t xml:space="preserve">2597534</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H89">
-        <v>321</v>
+        <v>948</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475476</t>
+          <t xml:space="preserve">311483621</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-13</t>
+          <t xml:space="preserve">2030-12-17</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5371,17 +5371,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyrlundsvej 11</t>
+          <t xml:space="preserve">Parkvej 8</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4140</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">5299044</t>
+          <t xml:space="preserve">2210082</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5390,16 +5390,16 @@
         </is>
       </c>
       <c r="H90">
-        <v>557</v>
+        <v>514</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475426</t>
+          <t xml:space="preserve">311483562</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-13</t>
+          <t xml:space="preserve">2030-12-17</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accisevej 1</t>
+          <t xml:space="preserve">Høgevej 9</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5441,25 +5441,25 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">5299241</t>
+          <t xml:space="preserve">9168077</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H91">
-        <v>734</v>
+        <v>530</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475433</t>
+          <t xml:space="preserve">311483961</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-13</t>
+          <t xml:space="preserve">2030-12-18</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boholtevej 85A</t>
+          <t xml:space="preserve">Høgevej 9</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5501,25 +5501,25 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">5302763</t>
+          <t xml:space="preserve">9168077</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H92">
-        <v>1324</v>
+        <v>1128</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475438</t>
+          <t xml:space="preserve">311483963</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-13</t>
+          <t xml:space="preserve">2030-12-18</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gymnasievej 22</t>
+          <t xml:space="preserve">Ørnevej 11</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5561,25 +5561,25 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">8638680</t>
+          <t xml:space="preserve">9168077</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H93">
-        <v>465</v>
+        <v>1356</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475851</t>
+          <t xml:space="preserve">311483967</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-16</t>
+          <t xml:space="preserve">2030-12-18</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gymnasievej 24</t>
+          <t xml:space="preserve">Ørnevej 15</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5621,25 +5621,25 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">9370842</t>
+          <t xml:space="preserve">9168077</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H94">
-        <v>784</v>
+        <v>885</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475844</t>
+          <t xml:space="preserve">311483967</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-16</t>
+          <t xml:space="preserve">2030-12-18</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mellemmarksvej 13</t>
+          <t xml:space="preserve">Aldersro 3</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">7010687</t>
+          <t xml:space="preserve">10175791</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5690,16 +5690,16 @@
         </is>
       </c>
       <c r="H95">
-        <v>722</v>
+        <v>354</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311477758</t>
+          <t xml:space="preserve">311484259</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-23</t>
+          <t xml:space="preserve">2030-12-21</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -5731,35 +5731,35 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slagterivej 12</t>
+          <t xml:space="preserve">Aldersro 3</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4681</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">5299224</t>
+          <t xml:space="preserve">10175791</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H96">
-        <v>1608</v>
+        <v>428</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483210</t>
+          <t xml:space="preserve">311484263</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-16</t>
+          <t xml:space="preserve">2030-12-21</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -5791,35 +5791,35 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 8</t>
+          <t xml:space="preserve">Byvej 33</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">4140</t>
+          <t xml:space="preserve">4682</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2210082</t>
+          <t xml:space="preserve">2597534</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H97">
-        <v>514</v>
+        <v>437</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483562</t>
+          <t xml:space="preserve">311484253</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-17</t>
+          <t xml:space="preserve">2030-12-21</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5851,17 +5851,17 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 31</t>
+          <t xml:space="preserve">Parkvej 13</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">4682</t>
+          <t xml:space="preserve">4140</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2597534</t>
+          <t xml:space="preserve">2209985</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5870,16 +5870,16 @@
         </is>
       </c>
       <c r="H98">
-        <v>600</v>
+        <v>1171</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483621</t>
+          <t xml:space="preserve">311484281</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-17</t>
+          <t xml:space="preserve">2030-12-21</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5911,35 +5911,35 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 31</t>
+          <t xml:space="preserve">Tigervej 20</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">4682</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2597534</t>
+          <t xml:space="preserve">2216228</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H99">
-        <v>948</v>
+        <v>504</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483621</t>
+          <t xml:space="preserve">311489560</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-17</t>
+          <t xml:space="preserve">2031-01-22</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørnevej 15</t>
+          <t xml:space="preserve">Frihedsvej 12</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -5981,25 +5981,25 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">9168077</t>
+          <t xml:space="preserve">5300128</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H100">
-        <v>885</v>
+        <v>803</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483967</t>
+          <t xml:space="preserve">311491356</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-18</t>
+          <t xml:space="preserve">2031-01-29</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høgevej 9</t>
+          <t xml:space="preserve">Søndre Centervej 112</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6041,25 +6041,25 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">9168077</t>
+          <t xml:space="preserve">7562165</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H101">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483961</t>
+          <t xml:space="preserve">311491358</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-18</t>
+          <t xml:space="preserve">2031-01-29</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6091,35 +6091,35 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høgevej 9</t>
+          <t xml:space="preserve">Højelsevej 1A</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4623</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">9168077</t>
+          <t xml:space="preserve">2214316</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H102">
-        <v>1128</v>
+        <v>266</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483963</t>
+          <t xml:space="preserve">311493260</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-18</t>
+          <t xml:space="preserve">2031-02-05</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørnevej 11</t>
+          <t xml:space="preserve">Rishøjvej 5</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6161,25 +6161,25 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">9168077</t>
+          <t xml:space="preserve">2219479</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H103">
-        <v>1356</v>
+        <v>689</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483967</t>
+          <t xml:space="preserve">311493605</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-18</t>
+          <t xml:space="preserve">2031-02-08</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6211,17 +6211,17 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aldersro 3</t>
+          <t xml:space="preserve">Ved Stadion 6</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">4681</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">10175791</t>
+          <t xml:space="preserve">100298242, 100298243</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6230,16 +6230,16 @@
         </is>
       </c>
       <c r="H104">
-        <v>354</v>
+        <v>2442</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311484259</t>
+          <t xml:space="preserve">311500199</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-21</t>
+          <t xml:space="preserve">2031-03-03</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aldersro 3</t>
+          <t xml:space="preserve">Vordingborgvej 124C</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6281,25 +6281,25 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">10175791</t>
+          <t xml:space="preserve">2595487</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H105">
-        <v>428</v>
+        <v>873</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311484263</t>
+          <t xml:space="preserve">311504181</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-21</t>
+          <t xml:space="preserve">2031-03-17</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6331,35 +6331,35 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 13</t>
+          <t xml:space="preserve">Vordingborgvej 124E</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">4140</t>
+          <t xml:space="preserve">4681</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209985</t>
+          <t xml:space="preserve">2595646</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H106">
-        <v>1171</v>
+        <v>1660</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311484281</t>
+          <t xml:space="preserve">311504185</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-21</t>
+          <t xml:space="preserve">2031-03-17</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -6391,35 +6391,35 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 33</t>
+          <t xml:space="preserve">Halvejen 14</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">4682</t>
+          <t xml:space="preserve">4632</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2597534</t>
+          <t xml:space="preserve">2589978</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H107">
-        <v>437</v>
+        <v>580</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311484253</t>
+          <t xml:space="preserve">311510338</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-21</t>
+          <t xml:space="preserve">2031-04-07</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -6451,35 +6451,35 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tigervej 20</t>
+          <t xml:space="preserve">Halvejen 4</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4632</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2216228</t>
+          <t xml:space="preserve">2589978</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H108">
-        <v>504</v>
+        <v>252</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311489560</t>
+          <t xml:space="preserve">311510337</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-22</t>
+          <t xml:space="preserve">2031-04-07</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -6511,17 +6511,17 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frihedsvej 12</t>
+          <t xml:space="preserve">Slimmingevej 78</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4100</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">5300128</t>
+          <t xml:space="preserve">2591660</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -6530,16 +6530,16 @@
         </is>
       </c>
       <c r="H109">
-        <v>803</v>
+        <v>313</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311491356</t>
+          <t xml:space="preserve">311510335</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-29</t>
+          <t xml:space="preserve">2031-04-07</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -6571,35 +6571,35 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Centervej 112</t>
+          <t xml:space="preserve">Møllevej 4</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4140</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">7562165</t>
+          <t xml:space="preserve">2209946</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H110">
-        <v>524</v>
+        <v>286</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311491358</t>
+          <t xml:space="preserve">311512262</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-29</t>
+          <t xml:space="preserve">2031-04-14</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -6631,35 +6631,35 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højelsevej 1A</t>
+          <t xml:space="preserve">Møllevej 11C</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">4623</t>
+          <t xml:space="preserve">4140</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2214316</t>
+          <t xml:space="preserve">100039640</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H111">
-        <v>266</v>
+        <v>1189</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311493260</t>
+          <t xml:space="preserve">311512586</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-05</t>
+          <t xml:space="preserve">2031-04-15</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -6691,17 +6691,17 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rishøjvej 5</t>
+          <t xml:space="preserve">Ahornvej 1B</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4632</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2219479</t>
+          <t xml:space="preserve">2591270</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -6710,16 +6710,16 @@
         </is>
       </c>
       <c r="H112">
-        <v>689</v>
+        <v>380</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311493605</t>
+          <t xml:space="preserve">311513452</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-08</t>
+          <t xml:space="preserve">2031-04-19</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -6751,17 +6751,17 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vordingborgvej 124C</t>
+          <t xml:space="preserve">Gartnervej 18</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">4681</t>
+          <t xml:space="preserve">4632</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2595487</t>
+          <t xml:space="preserve">8352544</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -6770,16 +6770,16 @@
         </is>
       </c>
       <c r="H113">
-        <v>873</v>
+        <v>485</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311504181</t>
+          <t xml:space="preserve">311513468</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-17</t>
+          <t xml:space="preserve">2031-04-19</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -6811,35 +6811,35 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vordingborgvej 124E</t>
+          <t xml:space="preserve">Marksvinget 22</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">4681</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2595646</t>
+          <t xml:space="preserve">5302628</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H114">
-        <v>1660</v>
+        <v>453</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311504185</t>
+          <t xml:space="preserve">311513379</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-17</t>
+          <t xml:space="preserve">2031-04-19</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -6871,35 +6871,35 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halvejen 14</t>
+          <t xml:space="preserve">Rønnevej 21</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">4632</t>
+          <t xml:space="preserve">4140</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2589978</t>
+          <t xml:space="preserve">2209908</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H115">
-        <v>580</v>
+        <v>422</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311510338</t>
+          <t xml:space="preserve">311513456</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-07</t>
+          <t xml:space="preserve">2031-04-19</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -6931,35 +6931,35 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halvejen 4</t>
+          <t xml:space="preserve">Kirkepladsen 2</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">4632</t>
+          <t xml:space="preserve">4681</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2589978</t>
+          <t xml:space="preserve">2594623</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H116">
-        <v>252</v>
+        <v>416</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311510337</t>
+          <t xml:space="preserve">311514520</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-07</t>
+          <t xml:space="preserve">2031-04-22</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -6991,17 +6991,17 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slimmingevej 78</t>
+          <t xml:space="preserve">Scheelsvej 2A</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">4100</t>
+          <t xml:space="preserve">4681</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2591660</t>
+          <t xml:space="preserve">2595960</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -7010,16 +7010,16 @@
         </is>
       </c>
       <c r="H117">
-        <v>313</v>
+        <v>1279</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311510335</t>
+          <t xml:space="preserve">311517451</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-07</t>
+          <t xml:space="preserve">2031-05-04</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7051,35 +7051,35 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevej 4</t>
+          <t xml:space="preserve">Skovvang 3</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">4140</t>
+          <t xml:space="preserve">4623</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209946</t>
+          <t xml:space="preserve">8940846</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H118">
-        <v>286</v>
+        <v>400</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311512262</t>
+          <t xml:space="preserve">311517474</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-14</t>
+          <t xml:space="preserve">2031-05-04</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7111,35 +7111,35 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevej 11C</t>
+          <t xml:space="preserve">Boholtevej 89</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">4140</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">100039640</t>
+          <t xml:space="preserve">5302765</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H119">
-        <v>1189</v>
+        <v>455</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311512586</t>
+          <t xml:space="preserve">311519300</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-15</t>
+          <t xml:space="preserve">2031-05-11</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -7171,17 +7171,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rønnevej 21</t>
+          <t xml:space="preserve">Egøjevej 72</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">4140</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209908</t>
+          <t xml:space="preserve">5301648</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -7190,16 +7190,16 @@
         </is>
       </c>
       <c r="H120">
-        <v>422</v>
+        <v>480</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311513456</t>
+          <t xml:space="preserve">311519301</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-19</t>
+          <t xml:space="preserve">2031-05-11</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7231,17 +7231,17 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ahornvej 1B</t>
+          <t xml:space="preserve">Ravnsborgvej 12</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">4632</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2591270</t>
+          <t xml:space="preserve">8038405</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -7250,16 +7250,16 @@
         </is>
       </c>
       <c r="H121">
-        <v>380</v>
+        <v>544</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311513452</t>
+          <t xml:space="preserve">311519303</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-19</t>
+          <t xml:space="preserve">2031-05-11</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marksvinget 22</t>
+          <t xml:space="preserve">Ravnsborgvej 14</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">5302628</t>
+          <t xml:space="preserve">8239899</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -7310,16 +7310,16 @@
         </is>
       </c>
       <c r="H122">
-        <v>453</v>
+        <v>611</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311513379</t>
+          <t xml:space="preserve">311519304</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-19</t>
+          <t xml:space="preserve">2031-05-11</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gartnervej 18</t>
+          <t xml:space="preserve">Vollerslevvej 12</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">8352544</t>
+          <t xml:space="preserve">7609591</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -7370,16 +7370,16 @@
         </is>
       </c>
       <c r="H123">
-        <v>485</v>
+        <v>285</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311513468</t>
+          <t xml:space="preserve">311519591</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-19</t>
+          <t xml:space="preserve">2031-05-11</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -7411,17 +7411,17 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkepladsen 2</t>
+          <t xml:space="preserve">Hovedgaden 65</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">4681</t>
+          <t xml:space="preserve">4140</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2594623</t>
+          <t xml:space="preserve">265067, 265068</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -7430,16 +7430,16 @@
         </is>
       </c>
       <c r="H124">
-        <v>416</v>
+        <v>2578</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311514520</t>
+          <t xml:space="preserve">311519776</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-22</t>
+          <t xml:space="preserve">2031-05-12</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -7471,17 +7471,17 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheelsvej 2A</t>
+          <t xml:space="preserve">Parkvej 2</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">4681</t>
+          <t xml:space="preserve">4140</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2595960</t>
+          <t xml:space="preserve">2209991</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -7490,16 +7490,16 @@
         </is>
       </c>
       <c r="H125">
-        <v>1279</v>
+        <v>520</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311517451</t>
+          <t xml:space="preserve">311521608</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-04</t>
+          <t xml:space="preserve">2031-05-20</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -7531,17 +7531,17 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvang 3</t>
+          <t xml:space="preserve">Søndre Badevej 1</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">4623</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940846</t>
+          <t xml:space="preserve">5300240</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -7550,16 +7550,16 @@
         </is>
       </c>
       <c r="H126">
-        <v>400</v>
+        <v>1275</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311517474</t>
+          <t xml:space="preserve">311527885</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-04</t>
+          <t xml:space="preserve">2031-06-14</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -7591,17 +7591,17 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egøjevej 72</t>
+          <t xml:space="preserve">Baunebjergvej 1C</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4623</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">5301648</t>
+          <t xml:space="preserve">2214307</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -7610,16 +7610,16 @@
         </is>
       </c>
       <c r="H127">
-        <v>480</v>
+        <v>2884</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311519301</t>
+          <t xml:space="preserve">311533128</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-11</t>
+          <t xml:space="preserve">2031-07-02</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -7651,35 +7651,35 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boholtevej 89</t>
+          <t xml:space="preserve">Baunebjergvej 1C</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4623</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">5302765</t>
+          <t xml:space="preserve">2214307</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H128">
-        <v>455</v>
+        <v>972</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311519300</t>
+          <t xml:space="preserve">311533129</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-11</t>
+          <t xml:space="preserve">2031-07-02</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -7711,35 +7711,35 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vollerslevvej 12</t>
+          <t xml:space="preserve">Lerbæk Torv 11</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">4632</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">7609591</t>
+          <t xml:space="preserve">2593904</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H129">
-        <v>285</v>
+        <v>704</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311519591</t>
+          <t xml:space="preserve">311533127</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-11</t>
+          <t xml:space="preserve">2031-07-02</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnsborgvej 12</t>
+          <t xml:space="preserve">Lerbæk Torv 12</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">8038405</t>
+          <t xml:space="preserve">268651</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -7790,16 +7790,16 @@
         </is>
       </c>
       <c r="H130">
-        <v>544</v>
+        <v>602</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311519303</t>
+          <t xml:space="preserve">311533123</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-11</t>
+          <t xml:space="preserve">2031-07-02</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnsborgvej 14</t>
+          <t xml:space="preserve">Lerbæk Torv 2</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -7841,25 +7841,25 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">8239899</t>
+          <t xml:space="preserve">268652, 268653</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H131">
-        <v>611</v>
+        <v>2677</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311519304</t>
+          <t xml:space="preserve">311533125</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-11</t>
+          <t xml:space="preserve">2031-07-02</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -7891,35 +7891,35 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 2</t>
+          <t xml:space="preserve">Nørre Boulevard 101</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">4140</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209991</t>
+          <t xml:space="preserve">5300077</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H132">
-        <v>520</v>
+        <v>1158</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311521608</t>
+          <t xml:space="preserve">311533130</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-20</t>
+          <t xml:space="preserve">2031-07-02</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Badevej 1</t>
+          <t xml:space="preserve">Nørre Boulevard 103</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -7961,25 +7961,25 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">5300240</t>
+          <t xml:space="preserve">5300077</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H133">
-        <v>1275</v>
+        <v>2139</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311527885</t>
+          <t xml:space="preserve">311533130</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-14</t>
+          <t xml:space="preserve">2031-07-02</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunebjergvej 1C</t>
+          <t xml:space="preserve">Fogedvej 4</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2214307</t>
+          <t xml:space="preserve">8738812</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -8030,16 +8030,16 @@
         </is>
       </c>
       <c r="H134">
-        <v>2884</v>
+        <v>511</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533128</t>
+          <t xml:space="preserve">311533507</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-02</t>
+          <t xml:space="preserve">2031-07-05</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunebjergvej 1C</t>
+          <t xml:space="preserve">Gemsevej 23</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8081,25 +8081,25 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2214307</t>
+          <t xml:space="preserve">8127101</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H135">
-        <v>972</v>
+        <v>557</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533129</t>
+          <t xml:space="preserve">311533512</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-02</t>
+          <t xml:space="preserve">2031-07-05</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -8131,35 +8131,35 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerbæk Torv 11</t>
+          <t xml:space="preserve">Gemsevej 25</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4623</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2593904</t>
+          <t xml:space="preserve">2212560</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H136">
-        <v>704</v>
+        <v>403</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533127</t>
+          <t xml:space="preserve">311533516</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-02</t>
+          <t xml:space="preserve">2031-07-05</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørre Boulevard 103</t>
+          <t xml:space="preserve">Klemmenstrupvej 31</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">5300077</t>
+          <t xml:space="preserve">7382834</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -8210,16 +8210,16 @@
         </is>
       </c>
       <c r="H137">
-        <v>2139</v>
+        <v>1002</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533130</t>
+          <t xml:space="preserve">311533492</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-02</t>
+          <t xml:space="preserve">2031-07-05</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørre Boulevard 101</t>
+          <t xml:space="preserve">Langelandsvej 70</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8261,25 +8261,25 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">5300077</t>
+          <t xml:space="preserve">2593898</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H138">
-        <v>1158</v>
+        <v>5774</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533130</t>
+          <t xml:space="preserve">311533502</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-02</t>
+          <t xml:space="preserve">2031-07-05</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -8311,30 +8311,30 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gemsevej 25</t>
+          <t xml:space="preserve">Langelandsvej 72</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">4623</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2212560</t>
+          <t xml:space="preserve">2593898</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H139">
-        <v>403</v>
+        <v>544</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533516</t>
+          <t xml:space="preserve">311533496</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -8371,17 +8371,17 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langelandsvej 70</t>
+          <t xml:space="preserve">Pogebanken 9</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4681</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2593898</t>
+          <t xml:space="preserve">8314790</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -8390,11 +8390,11 @@
         </is>
       </c>
       <c r="H140">
-        <v>5774</v>
+        <v>5811</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533502</t>
+          <t xml:space="preserve">311533528</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -8431,35 +8431,35 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langelandsvej 72</t>
+          <t xml:space="preserve">Pogebanken 16</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4681</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2593898</t>
+          <t xml:space="preserve">2595280</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H141">
-        <v>544</v>
+        <v>996</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533496</t>
+          <t xml:space="preserve">311538975</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-05</t>
+          <t xml:space="preserve">2031-08-04</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -8491,17 +8491,17 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klemmenstrupvej 31</t>
+          <t xml:space="preserve">Vedskøllevej 1A</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4681</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">7382834</t>
+          <t xml:space="preserve">8314762</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -8510,16 +8510,16 @@
         </is>
       </c>
       <c r="H142">
-        <v>1002</v>
+        <v>1551</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533492</t>
+          <t xml:space="preserve">311538960</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-05</t>
+          <t xml:space="preserve">2031-08-04</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -8551,35 +8551,35 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gemsevej 23</t>
+          <t xml:space="preserve">Vedskøllevej 1A</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">4623</t>
+          <t xml:space="preserve">4681</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">8127101</t>
+          <t xml:space="preserve">8314762</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H143">
-        <v>557</v>
+        <v>4950</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533512</t>
+          <t xml:space="preserve">311538960</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-05</t>
+          <t xml:space="preserve">2031-08-04</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pogebanken 9</t>
+          <t xml:space="preserve">Vedskøllevej 1A</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -8621,25 +8621,25 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">8314790</t>
+          <t xml:space="preserve">8314762</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H144">
-        <v>5811</v>
+        <v>906</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533528</t>
+          <t xml:space="preserve">311538960</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-05</t>
+          <t xml:space="preserve">2031-08-04</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -8671,17 +8671,17 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fogedvej 4</t>
+          <t xml:space="preserve">Ølbycenter 51</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">4623</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">8738812</t>
+          <t xml:space="preserve">2215752</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -8690,16 +8690,16 @@
         </is>
       </c>
       <c r="H145">
-        <v>511</v>
+        <v>2429</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533507</t>
+          <t xml:space="preserve">311538964</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-05</t>
+          <t xml:space="preserve">2031-08-04</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ølbycenter 51</t>
+          <t xml:space="preserve">Ølbyvej 50</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2215752</t>
+          <t xml:space="preserve">5301218</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -8750,11 +8750,11 @@
         </is>
       </c>
       <c r="H146">
-        <v>2429</v>
+        <v>3420</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311538964</t>
+          <t xml:space="preserve">311538952</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pogebanken 16</t>
+          <t xml:space="preserve">Billesborgvej 1</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2595280</t>
+          <t xml:space="preserve">2595904</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -8810,16 +8810,16 @@
         </is>
       </c>
       <c r="H147">
-        <v>996</v>
+        <v>7177</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311538975</t>
+          <t xml:space="preserve">311539441</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-04</t>
+          <t xml:space="preserve">2031-08-06</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -8851,35 +8851,35 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ølbyvej 50</t>
+          <t xml:space="preserve">Billesborgvej 1B</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4681</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">5301218</t>
+          <t xml:space="preserve">2595904</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H148">
-        <v>3420</v>
+        <v>650</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311538952</t>
+          <t xml:space="preserve">311539435</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-04</t>
+          <t xml:space="preserve">2031-08-06</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -8911,17 +8911,17 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vedskøllevej 1A</t>
+          <t xml:space="preserve">Hovedgaden 39</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve">4681</t>
+          <t xml:space="preserve">4140</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">8314762</t>
+          <t xml:space="preserve">2209661</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -8930,16 +8930,16 @@
         </is>
       </c>
       <c r="H149">
-        <v>1551</v>
+        <v>2435</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311538960</t>
+          <t xml:space="preserve">311539909</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-04</t>
+          <t xml:space="preserve">2031-08-10</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -8971,35 +8971,35 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vedskøllevej 1A</t>
+          <t xml:space="preserve">Hovedgaden 39</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">4681</t>
+          <t xml:space="preserve">4140</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">8314762</t>
+          <t xml:space="preserve">2209661</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H150">
-        <v>4950</v>
+        <v>720</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311538960</t>
+          <t xml:space="preserve">311539909</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-04</t>
+          <t xml:space="preserve">2031-08-10</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -9031,35 +9031,35 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vedskøllevej 1A</t>
+          <t xml:space="preserve">Hovedgaden 39</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">4681</t>
+          <t xml:space="preserve">4140</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">8314762</t>
+          <t xml:space="preserve">2209661</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H151">
-        <v>906</v>
+        <v>1218</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311538960</t>
+          <t xml:space="preserve">311539909</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-04</t>
+          <t xml:space="preserve">2031-08-10</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -9091,35 +9091,35 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billesborgvej 1</t>
+          <t xml:space="preserve">Hovedgaden 39</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve">4681</t>
+          <t xml:space="preserve">4140</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2595904</t>
+          <t xml:space="preserve">2209661</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H152">
-        <v>7177</v>
+        <v>1187</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539441</t>
+          <t xml:space="preserve">311539909</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-06</t>
+          <t xml:space="preserve">2031-08-10</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -9151,35 +9151,35 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billesborgvej 1B</t>
+          <t xml:space="preserve">Hovedgaden 39</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t xml:space="preserve">4681</t>
+          <t xml:space="preserve">4140</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2595904</t>
+          <t xml:space="preserve">2209661</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H153">
-        <v>650</v>
+        <v>1590</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539435</t>
+          <t xml:space="preserve">311539909</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-06</t>
+          <t xml:space="preserve">2031-08-10</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -9226,11 +9226,11 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H154">
-        <v>2435</v>
+        <v>3575</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -9271,35 +9271,35 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 39</t>
+          <t xml:space="preserve">Kirkestræde 22</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">4140</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209661</t>
+          <t xml:space="preserve">8948780</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H155">
-        <v>720</v>
+        <v>980</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539909</t>
+          <t xml:space="preserve">311540512</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-10</t>
+          <t xml:space="preserve">2031-08-12</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -9331,35 +9331,35 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 39</t>
+          <t xml:space="preserve">Kirkestræde 24</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">4140</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209661</t>
+          <t xml:space="preserve">8948780</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H156">
-        <v>1218</v>
+        <v>253</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539909</t>
+          <t xml:space="preserve">311540512</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-10</t>
+          <t xml:space="preserve">2031-08-12</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -9391,35 +9391,35 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 39</t>
+          <t xml:space="preserve">Gemsevej 19</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">4140</t>
+          <t xml:space="preserve">4623</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209661</t>
+          <t xml:space="preserve">2212648</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H157">
-        <v>1187</v>
+        <v>443</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539909</t>
+          <t xml:space="preserve">311540701</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-10</t>
+          <t xml:space="preserve">2031-08-13</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -9451,35 +9451,35 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 39</t>
+          <t xml:space="preserve">Gymnasievej 8</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">4140</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209661</t>
+          <t xml:space="preserve">100040993</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H158">
-        <v>1590</v>
+        <v>756</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539909</t>
+          <t xml:space="preserve">311543562</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-10</t>
+          <t xml:space="preserve">2031-08-26</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -9511,35 +9511,35 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 39</t>
+          <t xml:space="preserve">Fændediget 4</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t xml:space="preserve">4140</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209661</t>
+          <t xml:space="preserve">5299406</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H159">
-        <v>3575</v>
+        <v>481</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539909</t>
+          <t xml:space="preserve">311544545</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-10</t>
+          <t xml:space="preserve">2031-08-31</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -9571,17 +9571,17 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkestræde 24</t>
+          <t xml:space="preserve">Skovvang 6</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4623</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">8948780</t>
+          <t xml:space="preserve">8940846</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -9590,16 +9590,16 @@
         </is>
       </c>
       <c r="H160">
-        <v>253</v>
+        <v>8394</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540512</t>
+          <t xml:space="preserve">311544560</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-12</t>
+          <t xml:space="preserve">2031-08-31</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -9631,35 +9631,35 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkestræde 22</t>
+          <t xml:space="preserve">Lidemarksvej 97A</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4632</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">8948780</t>
+          <t xml:space="preserve">2589978</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H161">
-        <v>980</v>
+        <v>390</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540512</t>
+          <t xml:space="preserve">311545404</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-12</t>
+          <t xml:space="preserve">2031-09-02</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -9691,35 +9691,35 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gemsevej 19</t>
+          <t xml:space="preserve">Lidemarksvej 97D</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t xml:space="preserve">4623</t>
+          <t xml:space="preserve">4632</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2212648</t>
+          <t xml:space="preserve">2589978</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H162">
-        <v>443</v>
+        <v>390</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540701</t>
+          <t xml:space="preserve">311545404</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-13</t>
+          <t xml:space="preserve">2031-09-02</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -9751,35 +9751,35 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gymnasievej 8</t>
+          <t xml:space="preserve">Lidemarksvej 97G</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4632</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">100040993</t>
+          <t xml:space="preserve">2589978</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H163">
-        <v>756</v>
+        <v>254</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311543562</t>
+          <t xml:space="preserve">311545528</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-26</t>
+          <t xml:space="preserve">2031-09-02</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -9811,17 +9811,17 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fændediget 4</t>
+          <t xml:space="preserve">Vemmedrupvej 235</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4632</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">5299406</t>
+          <t xml:space="preserve">2590529</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -9830,16 +9830,16 @@
         </is>
       </c>
       <c r="H164">
-        <v>481</v>
+        <v>590</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311544545</t>
+          <t xml:space="preserve">311549276</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-31</t>
+          <t xml:space="preserve">2031-09-20</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -9871,35 +9871,35 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvang 6</t>
+          <t xml:space="preserve">Vestergade 3A</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t xml:space="preserve">4623</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940846</t>
+          <t xml:space="preserve">5298617</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H165">
-        <v>8394</v>
+        <v>386</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311544560</t>
+          <t xml:space="preserve">311549360</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-31</t>
+          <t xml:space="preserve">2031-09-20</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -9931,35 +9931,35 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lidemarksvej 97A</t>
+          <t xml:space="preserve">Buen 21</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve">4632</t>
+          <t xml:space="preserve">4623</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2589978</t>
+          <t xml:space="preserve">2214735</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H166">
-        <v>390</v>
+        <v>416</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311545404</t>
+          <t xml:space="preserve">311550074</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-02</t>
+          <t xml:space="preserve">2031-09-22</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -9991,35 +9991,35 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lidemarksvej 97D</t>
+          <t xml:space="preserve">Buen 7</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">4632</t>
+          <t xml:space="preserve">4623</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2589978</t>
+          <t xml:space="preserve">2214735</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H167">
-        <v>390</v>
+        <v>312</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311545404</t>
+          <t xml:space="preserve">311550074</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-02</t>
+          <t xml:space="preserve">2031-09-22</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -10051,35 +10051,35 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lidemarksvej 97G</t>
+          <t xml:space="preserve">Ølbycenter 104</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t xml:space="preserve">4632</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2589978</t>
+          <t xml:space="preserve">9223091</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H168">
-        <v>254</v>
+        <v>5045</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311545528</t>
+          <t xml:space="preserve">311550306</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-02</t>
+          <t xml:space="preserve">2031-09-23</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vemmedrupvej 235</t>
+          <t xml:space="preserve">Halvejen 2</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -10121,25 +10121,25 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2590529</t>
+          <t xml:space="preserve">2589978</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H169">
-        <v>590</v>
+        <v>6715</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549276</t>
+          <t xml:space="preserve">311561871</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-20</t>
+          <t xml:space="preserve">2031-11-15</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -10171,35 +10171,35 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 3A</t>
+          <t xml:space="preserve">Halvejen 2</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4632</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298617</t>
+          <t xml:space="preserve">2589978</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H170">
-        <v>386</v>
+        <v>2017</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549360</t>
+          <t xml:space="preserve">311561871</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-20</t>
+          <t xml:space="preserve">2031-11-15</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -10231,35 +10231,35 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buen 7</t>
+          <t xml:space="preserve">Halvejen 2</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t xml:space="preserve">4623</t>
+          <t xml:space="preserve">4632</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2214735</t>
+          <t xml:space="preserve">2589978</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H171">
-        <v>312</v>
+        <v>1359</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311550074</t>
+          <t xml:space="preserve">311561871</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-22</t>
+          <t xml:space="preserve">2031-11-15</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -10291,35 +10291,35 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buen 21</t>
+          <t xml:space="preserve">Møllevej 2</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t xml:space="preserve">4623</t>
+          <t xml:space="preserve">4140</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2214735</t>
+          <t xml:space="preserve">100013861</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H172">
-        <v>416</v>
+        <v>3292</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311550074</t>
+          <t xml:space="preserve">311566593</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-22</t>
+          <t xml:space="preserve">2031-12-07</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -10351,7 +10351,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ølbycenter 104</t>
+          <t xml:space="preserve">Karlemosevej 48</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -10361,7 +10361,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">9223091</t>
+          <t xml:space="preserve">2215842</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -10370,16 +10370,16 @@
         </is>
       </c>
       <c r="H173">
-        <v>5045</v>
+        <v>676</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311550306</t>
+          <t xml:space="preserve">311568002</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-23</t>
+          <t xml:space="preserve">2031-12-15</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -10411,17 +10411,17 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halvejen 2</t>
+          <t xml:space="preserve">Torvet 1</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t xml:space="preserve">4632</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2589978</t>
+          <t xml:space="preserve">266956, 266957</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -10430,16 +10430,16 @@
         </is>
       </c>
       <c r="H174">
-        <v>6715</v>
+        <v>7502</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561871</t>
+          <t xml:space="preserve">311570444</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-15</t>
+          <t xml:space="preserve">2032-01-04</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -10471,17 +10471,17 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halvejen 2</t>
+          <t xml:space="preserve">Torvet 1</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t xml:space="preserve">4632</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2589978</t>
+          <t xml:space="preserve">266956, 266958</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -10490,16 +10490,16 @@
         </is>
       </c>
       <c r="H175">
-        <v>2017</v>
+        <v>4799</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561871</t>
+          <t xml:space="preserve">311570444</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-15</t>
+          <t xml:space="preserve">2032-01-04</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -10531,35 +10531,35 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halvejen 2</t>
+          <t xml:space="preserve">Søbækvej 2</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t xml:space="preserve">4632</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2589978</t>
+          <t xml:space="preserve">9492257</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H176">
-        <v>1359</v>
+        <v>856</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561871</t>
+          <t xml:space="preserve">311571109</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-15</t>
+          <t xml:space="preserve">2032-01-07</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -10591,17 +10591,17 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevej 2</t>
+          <t xml:space="preserve">Rasmussensvej 23</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t xml:space="preserve">4140</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">100013861</t>
+          <t xml:space="preserve">8314862</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -10610,16 +10610,16 @@
         </is>
       </c>
       <c r="H177">
-        <v>3292</v>
+        <v>4490</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566593</t>
+          <t xml:space="preserve">311574331</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-07</t>
+          <t xml:space="preserve">2032-01-25</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -10651,7 +10651,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karlemosevej 48</t>
+          <t xml:space="preserve">Gymnasievej 10</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -10661,7 +10661,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2215842</t>
+          <t xml:space="preserve">5301791</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -10670,16 +10670,16 @@
         </is>
       </c>
       <c r="H178">
-        <v>676</v>
+        <v>5745</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568002</t>
+          <t xml:space="preserve">311574812</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-15</t>
+          <t xml:space="preserve">2032-01-26</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søbækvej 2</t>
+          <t xml:space="preserve">Gymnasievej 10</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -10721,25 +10721,25 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">9492257</t>
+          <t xml:space="preserve">5301791</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H179">
-        <v>856</v>
+        <v>1353</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571109</t>
+          <t xml:space="preserve">311574812</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-07</t>
+          <t xml:space="preserve">2032-01-26</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -10771,17 +10771,17 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rasmussensvej 23</t>
+          <t xml:space="preserve">Jernhøj 1</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4140</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">8314862</t>
+          <t xml:space="preserve">100041898</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -10790,16 +10790,16 @@
         </is>
       </c>
       <c r="H180">
-        <v>4490</v>
+        <v>2276</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311574331</t>
+          <t xml:space="preserve">311575628</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-25</t>
+          <t xml:space="preserve">2032-01-31</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -10831,7 +10831,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gymnasievej 10</t>
+          <t xml:space="preserve">Skolevej 1</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">5301791</t>
+          <t xml:space="preserve">2219385</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -10850,16 +10850,16 @@
         </is>
       </c>
       <c r="H181">
-        <v>5745</v>
+        <v>1776</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311574812</t>
+          <t xml:space="preserve">311578008</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-26</t>
+          <t xml:space="preserve">2032-02-10</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gymnasievej 10</t>
+          <t xml:space="preserve">Skolevej 1</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -10901,7 +10901,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">5301791</t>
+          <t xml:space="preserve">2219385</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -10910,16 +10910,16 @@
         </is>
       </c>
       <c r="H182">
-        <v>1353</v>
+        <v>701</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311574812</t>
+          <t xml:space="preserve">311578008</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-26</t>
+          <t xml:space="preserve">2032-02-10</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -10951,35 +10951,35 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernhøj 1</t>
+          <t xml:space="preserve">Skolevej 1</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t xml:space="preserve">4140</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">100041898</t>
+          <t xml:space="preserve">2219385</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H183">
-        <v>2276</v>
+        <v>1695</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311575628</t>
+          <t xml:space="preserve">311578008</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-31</t>
+          <t xml:space="preserve">2032-02-10</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -11026,11 +11026,11 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H184">
-        <v>1776</v>
+        <v>933</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -11086,11 +11086,11 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H185">
-        <v>701</v>
+        <v>966</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
@@ -11146,11 +11146,11 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H186">
-        <v>1695</v>
+        <v>1139</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
@@ -11206,11 +11206,11 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H187">
-        <v>933</v>
+        <v>846</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
@@ -11251,35 +11251,35 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 1</t>
+          <t xml:space="preserve">Vindegårdsvej 1</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4632</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2219385</t>
+          <t xml:space="preserve">8940960</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H188">
-        <v>966</v>
+        <v>4713</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311578008</t>
+          <t xml:space="preserve">311582210</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-10</t>
+          <t xml:space="preserve">2032-03-03</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -11311,17 +11311,17 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 1</t>
+          <t xml:space="preserve">Vindegårdsvej 1</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4632</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2219385</t>
+          <t xml:space="preserve">8940960</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -11330,16 +11330,16 @@
         </is>
       </c>
       <c r="H189">
-        <v>1139</v>
+        <v>629</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311578008</t>
+          <t xml:space="preserve">311582210</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-10</t>
+          <t xml:space="preserve">2032-03-03</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -11371,7 +11371,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 1</t>
+          <t xml:space="preserve">Allegade 2A</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -11381,25 +11381,25 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2219385</t>
+          <t xml:space="preserve">5298857</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H190">
-        <v>846</v>
+        <v>972</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311578008</t>
+          <t xml:space="preserve">311583248</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-10</t>
+          <t xml:space="preserve">2032-03-08</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -11431,35 +11431,35 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vindegårdsvej 1</t>
+          <t xml:space="preserve">Kirkestræde 28</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t xml:space="preserve">4632</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940960</t>
+          <t xml:space="preserve">5298849</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H191">
-        <v>4713</v>
+        <v>876</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582210</t>
+          <t xml:space="preserve">311583573</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-03</t>
+          <t xml:space="preserve">2032-03-09</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -11491,35 +11491,35 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vindegårdsvej 1</t>
+          <t xml:space="preserve">Nørregade 43</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t xml:space="preserve">4632</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940960</t>
+          <t xml:space="preserve">5298858</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H192">
-        <v>629</v>
+        <v>1657</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582210</t>
+          <t xml:space="preserve">311583564</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-03</t>
+          <t xml:space="preserve">2032-03-09</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allegade 2A</t>
+          <t xml:space="preserve">Nørregade 43</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -11561,7 +11561,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298857</t>
+          <t xml:space="preserve">5298858</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -11570,16 +11570,16 @@
         </is>
       </c>
       <c r="H193">
-        <v>972</v>
+        <v>1651</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311583248</t>
+          <t xml:space="preserve">311583564</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-08</t>
+          <t xml:space="preserve">2032-03-09</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -11611,7 +11611,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkestræde 28</t>
+          <t xml:space="preserve">Lerbæk Torv 30</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -11621,7 +11621,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298849</t>
+          <t xml:space="preserve">268650, 268651</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -11630,16 +11630,16 @@
         </is>
       </c>
       <c r="H194">
-        <v>876</v>
+        <v>1122</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311583573</t>
+          <t xml:space="preserve">311584438</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-09</t>
+          <t xml:space="preserve">2032-03-11</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -11671,7 +11671,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 43</t>
+          <t xml:space="preserve">Sygehusvej 25</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -11681,25 +11681,25 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298858</t>
+          <t xml:space="preserve">5298996</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H195">
-        <v>1657</v>
+        <v>499</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311583564</t>
+          <t xml:space="preserve">311584350</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-09</t>
+          <t xml:space="preserve">2032-03-11</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 43</t>
+          <t xml:space="preserve">Sygehusvej 25</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -11741,25 +11741,25 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298858</t>
+          <t xml:space="preserve">5298996</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H196">
-        <v>1651</v>
+        <v>347</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311583564</t>
+          <t xml:space="preserve">311584350</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-09</t>
+          <t xml:space="preserve">2032-03-11</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -11806,11 +11806,11 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H197">
-        <v>499</v>
+        <v>800</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sygehusvej 25</t>
+          <t xml:space="preserve">Københavnsvej 265</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -11861,25 +11861,25 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298996</t>
+          <t xml:space="preserve">8195911</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H198">
-        <v>347</v>
+        <v>292</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311584350</t>
+          <t xml:space="preserve">311586697</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-11</t>
+          <t xml:space="preserve">2032-03-21</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -11911,7 +11911,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sygehusvej 25</t>
+          <t xml:space="preserve">Nylandsvej 115</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -11921,25 +11921,25 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298996</t>
+          <t xml:space="preserve">8013178</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H199">
-        <v>800</v>
+        <v>418</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311584350</t>
+          <t xml:space="preserve">311597197</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-11</t>
+          <t xml:space="preserve">2032-05-03</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -11971,7 +11971,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Københavnsvej 265</t>
+          <t xml:space="preserve">Nylandsvej 117</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -11981,25 +11981,25 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">8195911</t>
+          <t xml:space="preserve">8013178</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H200">
-        <v>292</v>
+        <v>350</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586697</t>
+          <t xml:space="preserve">311597197</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-21</t>
+          <t xml:space="preserve">2032-05-03</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -12031,7 +12031,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nylandsvej 115</t>
+          <t xml:space="preserve">Ved Stadion 10</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">8013178</t>
+          <t xml:space="preserve">265103</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -12050,11 +12050,11 @@
         </is>
       </c>
       <c r="H201">
-        <v>418</v>
+        <v>298</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311597197</t>
+          <t xml:space="preserve">311597207</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nylandsvej 117</t>
+          <t xml:space="preserve">Fuglebæk Alle 3</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -12101,25 +12101,25 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">8013178</t>
+          <t xml:space="preserve">100090478</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H202">
-        <v>350</v>
+        <v>2788</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311597197</t>
+          <t xml:space="preserve">311626787</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-03</t>
+          <t xml:space="preserve">2032-09-09</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglebæk Alle 3</t>
+          <t xml:space="preserve">Bag Haverne 1</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -12161,7 +12161,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">100090478</t>
+          <t xml:space="preserve">5299445</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -12170,16 +12170,16 @@
         </is>
       </c>
       <c r="H203">
-        <v>2788</v>
+        <v>1589</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311626787</t>
+          <t xml:space="preserve">311637067</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-09</t>
+          <t xml:space="preserve">2032-10-20</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bag Haverne 1</t>
+          <t xml:space="preserve">Rishøjvej 1C</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -12221,7 +12221,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">5299445</t>
+          <t xml:space="preserve">2219342</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -12230,16 +12230,16 @@
         </is>
       </c>
       <c r="H204">
-        <v>1589</v>
+        <v>1190</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311637067</t>
+          <t xml:space="preserve">311719130</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-20</t>
+          <t xml:space="preserve">2033-11-01</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -12271,7 +12271,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rishøjvej 1C</t>
+          <t xml:space="preserve">Ravnsborgvej 3D</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -12281,7 +12281,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2219342</t>
+          <t xml:space="preserve">8960384</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -12290,16 +12290,16 @@
         </is>
       </c>
       <c r="H205">
-        <v>1190</v>
+        <v>1820</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719130</t>
+          <t xml:space="preserve">311724352</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-01</t>
+          <t xml:space="preserve">2033-11-23</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -12331,35 +12331,35 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnsborgvej 3D</t>
+          <t xml:space="preserve">Bjæverskovhusene 34</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4632</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">8960384</t>
+          <t xml:space="preserve">271380, 271381</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H206">
-        <v>1820</v>
+        <v>1104</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311724352</t>
+          <t xml:space="preserve">311725609</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-23</t>
+          <t xml:space="preserve">2033-11-29</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311777231</t>
+          <t xml:space="preserve">311777229</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tigervej 8</t>
+          <t xml:space="preserve">Byledet 66</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">5300146</t>
+          <t xml:space="preserve">5302818</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -12650,11 +12650,11 @@
         </is>
       </c>
       <c r="H211">
-        <v>309</v>
+        <v>529</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918711</t>
+          <t xml:space="preserve">311918710</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -12706,15 +12706,15 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H212">
-        <v>1034</v>
+        <v>309</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918712</t>
+          <t xml:space="preserve">311918711</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -12751,7 +12751,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byledet 66</t>
+          <t xml:space="preserve">Tigervej 8</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -12761,20 +12761,20 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">5302818</t>
+          <t xml:space="preserve">5300146</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H213">
-        <v>529</v>
+        <v>1034</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918710</t>
+          <t xml:space="preserve">311918712</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">

--- a/public/exports/29189374.xlsx
+++ b/public/exports/29189374.xlsx
@@ -3474,7 +3474,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311165256</t>
+          <t xml:space="preserve">311165259</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">

--- a/public/exports/29189374.xlsx
+++ b/public/exports/29189374.xlsx
@@ -3714,7 +3714,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311461620</t>
+          <t xml:space="preserve">311461621</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311461620</t>
+          <t xml:space="preserve">311461621</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311461926</t>
+          <t xml:space="preserve">311461967</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311510338</t>
+          <t xml:space="preserve">311510337</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311510335</t>
+          <t xml:space="preserve">311510336</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539441</t>
+          <t xml:space="preserve">311539435</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539909</t>
+          <t xml:space="preserve">311539849</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -8994,7 +8994,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539909</t>
+          <t xml:space="preserve">311539849</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -9054,7 +9054,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539909</t>
+          <t xml:space="preserve">311539849</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539909</t>
+          <t xml:space="preserve">311539849</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539909</t>
+          <t xml:space="preserve">311539849</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539909</t>
+          <t xml:space="preserve">311539849</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">

--- a/public/exports/29189374.xlsx
+++ b/public/exports/29189374.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L213"/>
+  <dimension ref="A1:M213"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -904,10 +974,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -964,10 +1039,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1024,10 +1104,15 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1084,10 +1169,15 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1144,10 +1234,15 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1204,10 +1299,15 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1264,10 +1364,15 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1324,10 +1429,15 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1384,10 +1494,15 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1444,10 +1559,15 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1504,10 +1624,15 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1564,10 +1689,15 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1624,10 +1754,15 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1684,10 +1819,15 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1744,10 +1884,15 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1804,10 +1949,15 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1864,10 +2014,15 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1924,10 +2079,15 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1984,10 +2144,15 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2044,10 +2209,15 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2104,10 +2274,15 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2164,10 +2339,15 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2224,10 +2404,15 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2284,10 +2469,15 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2344,10 +2534,15 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2404,10 +2599,15 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2464,10 +2664,15 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2524,10 +2729,15 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2584,10 +2794,15 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2644,10 +2859,15 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2704,10 +2924,15 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2764,10 +2989,15 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2824,10 +3054,15 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2884,10 +3119,15 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2944,10 +3184,15 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2999,15 +3244,20 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rådgivende ingeniørfirma</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2014-04-22</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3059,15 +3309,20 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-11-29</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3119,15 +3374,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-02-04</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3179,15 +3439,20 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-02-04</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3239,15 +3504,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-08-08</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3299,15 +3569,20 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-08-08</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3359,15 +3634,20 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-08-08</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3419,15 +3699,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t xml:space="preserve">Topdahl ApS</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-03-17</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3479,15 +3764,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t xml:space="preserve">Topdahl ApS</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-03-17</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Promana A/S</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-02-13</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3599,15 +3894,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Just A/S Rådgivende Ingeniørfirma</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-11-13</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3659,15 +3959,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-17</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3714,20 +4019,25 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311461621</t>
+          <t xml:space="preserve">311461620</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-17</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3774,20 +4084,25 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311461621</t>
+          <t xml:space="preserve">311461620</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-17</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3839,15 +4154,20 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-17</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3894,20 +4214,25 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311461967</t>
+          <t xml:space="preserve">311461926</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-18</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3959,15 +4284,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-18</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-21</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-20</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4199,15 +4544,20 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-23</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4259,15 +4609,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-23</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4319,15 +4674,20 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-23</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4379,15 +4739,20 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-11-09</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4439,15 +4804,20 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-11-10</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4499,15 +4869,20 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-11-11</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4559,15 +4934,20 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-11-13</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4619,15 +4999,20 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-11-13</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4679,15 +5064,20 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-11-13</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4739,15 +5129,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-11-13</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4799,15 +5194,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-11-13</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4859,15 +5259,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-11-13</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4919,15 +5324,20 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-11-13</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4979,15 +5389,20 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-11-13</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5039,15 +5454,20 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-11-16</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5099,15 +5519,20 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-11-16</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5159,15 +5584,20 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-11-23</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5219,15 +5649,20 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-16</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5279,15 +5714,20 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-17</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5339,15 +5779,20 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-17</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5399,15 +5844,20 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-17</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5459,15 +5909,20 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-18</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5519,15 +5974,20 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-18</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5579,15 +6039,20 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-18</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5639,15 +6104,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-18</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5699,15 +6169,20 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-21</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5759,15 +6234,20 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-21</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5819,15 +6299,20 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-21</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5879,15 +6364,20 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-21</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5939,15 +6429,20 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-01-22</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5999,15 +6494,20 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-01-29</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6059,15 +6559,20 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-01-29</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6119,15 +6624,20 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-05</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6179,15 +6689,20 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-08</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6239,15 +6754,20 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-03</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6299,15 +6819,20 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-17</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6359,15 +6884,20 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-17</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6419,15 +6949,20 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-07</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6479,15 +7014,20 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-07</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6539,15 +7079,20 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-07</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6599,15 +7144,20 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-14</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6659,15 +7209,20 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-15</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6719,15 +7274,20 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-19</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6779,15 +7339,20 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-19</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6839,15 +7404,20 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-19</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6899,15 +7469,20 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-19</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6959,15 +7534,20 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-22</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7019,15 +7599,20 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-04</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7079,15 +7664,20 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-04</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7139,15 +7729,20 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-11</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7199,15 +7794,20 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-11</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7259,15 +7859,20 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-11</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7319,15 +7924,20 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-11</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7379,15 +7989,20 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-11</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7439,15 +8054,20 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-12</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7499,15 +8119,20 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-20</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7559,15 +8184,20 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-14</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7619,15 +8249,20 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-02</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7679,15 +8314,20 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-02</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7739,15 +8379,20 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-02</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7799,15 +8444,20 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-02</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7859,15 +8509,20 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-02</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7919,15 +8574,20 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-02</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7979,15 +8639,20 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-02</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8039,15 +8704,20 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-05</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8099,15 +8769,20 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-05</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8159,15 +8834,20 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-05</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8219,15 +8899,20 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-05</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8279,15 +8964,20 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-05</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8339,15 +9029,20 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-05</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8399,15 +9094,20 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-05</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8459,15 +9159,20 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-04</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8519,15 +9224,20 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-04</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8579,15 +9289,20 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-04</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8639,15 +9354,20 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-04</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8699,15 +9419,20 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-04</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8759,15 +9484,20 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-04</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8819,15 +9549,20 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-06</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8879,15 +9614,20 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-06</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8939,15 +9679,20 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-10</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8999,15 +9744,20 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-10</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9059,15 +9809,20 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-10</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9119,15 +9874,20 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-10</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9179,15 +9939,20 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-10</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9239,15 +10004,20 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-10</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9299,15 +10069,20 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-12</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9359,15 +10134,20 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-12</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9419,15 +10199,20 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-13</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9479,15 +10264,20 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-26</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9539,15 +10329,20 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-31</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9599,15 +10394,20 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-31</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9659,15 +10459,20 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-02</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9719,15 +10524,20 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-02</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9779,15 +10589,20 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-02</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9839,15 +10654,20 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-20</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9899,15 +10719,20 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-20</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9959,15 +10784,20 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-22</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10019,15 +10849,20 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-22</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10079,15 +10914,20 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-23</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10139,15 +10979,20 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-15</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10199,15 +11044,20 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-15</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10259,15 +11109,20 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-15</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10319,15 +11174,20 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-07</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10379,15 +11239,20 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-15</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10439,15 +11304,20 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-04</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10499,15 +11369,20 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-04</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10559,15 +11434,20 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-07</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10619,15 +11499,20 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-25</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10679,15 +11564,20 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-26</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10739,15 +11629,20 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-26</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10799,15 +11694,20 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-31</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10859,15 +11759,20 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-02-10</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10919,15 +11824,20 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-02-10</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10979,15 +11889,20 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-02-10</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11039,15 +11954,20 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-02-10</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11099,15 +12019,20 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-02-10</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11159,15 +12084,20 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-02-10</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11219,15 +12149,20 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-02-10</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11279,15 +12214,20 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-03</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11339,15 +12279,20 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-03</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11399,15 +12344,20 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-08</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11459,15 +12409,20 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-09</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11519,15 +12474,20 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-09</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11579,15 +12539,20 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-09</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11639,15 +12604,20 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-11</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11699,15 +12669,20 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-11</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11759,15 +12734,20 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-11</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11819,15 +12799,20 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-11</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11879,15 +12864,20 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-21</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11939,15 +12929,20 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-03</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11999,15 +12994,20 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-03</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12059,15 +13059,20 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-03</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12119,15 +13124,20 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-09-09</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12179,15 +13189,20 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-10-20</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12239,15 +13254,20 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
+          <t xml:space="preserve">Inspec ApS</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-01</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12299,15 +13319,20 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-23</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12359,15 +13384,20 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-29</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12419,15 +13449,20 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-01-05</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12479,15 +13514,20 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-08-09</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12539,15 +13579,20 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
+          <t xml:space="preserve">Norca Aps</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-24</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12599,15 +13644,20 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
+          <t xml:space="preserve">Inspec ApS</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-01</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12659,15 +13709,20 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-12</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12714,20 +13769,25 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918711</t>
+          <t xml:space="preserve">311918714</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-12</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12779,21 +13839,26 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-12</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L213" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L213"/>
+  <autoFilter ref="A1:M213"/>
 </worksheet>
 </file>
--- a/public/exports/29189374.xlsx
+++ b/public/exports/29189374.xlsx
@@ -1201,7 +1201,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norsvej 2</t>
+          <t xml:space="preserve">Nørre Boulevard 107</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">8765343</t>
+          <t xml:space="preserve">5300078</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="H19">
-        <v>2988</v>
+        <v>1287</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norsvej 2</t>
+          <t xml:space="preserve">Overdrevsvejen 26</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1276,16 +1276,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">8765343</t>
+          <t xml:space="preserve">5302896</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H20">
-        <v>2512</v>
+        <v>395</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norsvej 2</t>
+          <t xml:space="preserve">Parkvej 120</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1341,16 +1341,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">8765343</t>
+          <t xml:space="preserve">100165388</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H21">
-        <v>1540</v>
+        <v>1896</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norsvej 2</t>
+          <t xml:space="preserve">Ravnsborgvej 1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1406,16 +1406,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">8765343</t>
+          <t xml:space="preserve">718828, 2594249</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H22">
-        <v>2844</v>
+        <v>1067</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norsvej 2</t>
+          <t xml:space="preserve">Ravnsborgvej 3A</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1471,16 +1471,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">8765343</t>
+          <t xml:space="preserve">718738, 2594250</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H23">
-        <v>1874</v>
+        <v>1898</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norsvej 6</t>
+          <t xml:space="preserve">Ravnsborgvej 3B</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1536,16 +1536,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">8769222</t>
+          <t xml:space="preserve">100450727</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="H24">
-        <v>987</v>
+        <v>1399</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørre Boulevard 107</t>
+          <t xml:space="preserve">Sygehusvej 25</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1601,16 +1601,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5300078</t>
+          <t xml:space="preserve">5298996</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H25">
-        <v>1287</v>
+        <v>1261</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overdrevsvejen 26</t>
+          <t xml:space="preserve">Sygehusvej 25</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1666,16 +1666,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5302896</t>
+          <t xml:space="preserve">5298996</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H26">
-        <v>395</v>
+        <v>346</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 120</t>
+          <t xml:space="preserve">Sygehusvej 25A</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1731,16 +1731,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">100165388</t>
+          <t xml:space="preserve">5298996</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H27">
-        <v>1896</v>
+        <v>2331</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnsborgvej 1</t>
+          <t xml:space="preserve">Søbækvej 1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1796,16 +1796,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">718828, 2594249</t>
+          <t xml:space="preserve">7781206</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H28">
-        <v>1067</v>
+        <v>1240</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnsborgvej 3A</t>
+          <t xml:space="preserve">Søndre Alle 6</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1861,16 +1861,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">718738, 2594250</t>
+          <t xml:space="preserve">5301281</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H29">
-        <v>1898</v>
+        <v>577</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnsborgvej 3B</t>
+          <t xml:space="preserve">Søndre Alle 6</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1926,16 +1926,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">100450727</t>
+          <t xml:space="preserve">5301281</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H30">
-        <v>1399</v>
+        <v>340</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sygehusvej 25</t>
+          <t xml:space="preserve">Tigervej 20</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1991,16 +1991,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298996</t>
+          <t xml:space="preserve">2216228</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H31">
-        <v>1261</v>
+        <v>259</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sygehusvej 25</t>
+          <t xml:space="preserve">Tigervej 20</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2056,16 +2056,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298996</t>
+          <t xml:space="preserve">2216228</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H32">
-        <v>346</v>
+        <v>259</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2111,26 +2111,26 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sygehusvej 25A</t>
+          <t xml:space="preserve">Tornbjergvej 42</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4623</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298996</t>
+          <t xml:space="preserve">2211891</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H33">
-        <v>2331</v>
+        <v>583</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søbækvej 1</t>
+          <t xml:space="preserve">Ved Stadion 4</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">7781206</t>
+          <t xml:space="preserve">8314857</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="H34">
-        <v>1240</v>
+        <v>387</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Alle 6</t>
+          <t xml:space="preserve">Ved Stadion 4</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2251,16 +2251,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">5301281</t>
+          <t xml:space="preserve">8314857</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H35">
-        <v>577</v>
+        <v>1222</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Alle 6</t>
+          <t xml:space="preserve">Ved Stadion 4</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2316,16 +2316,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">5301281</t>
+          <t xml:space="preserve">8314857</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H36">
-        <v>340</v>
+        <v>271</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2371,26 +2371,26 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tigervej 20</t>
+          <t xml:space="preserve">Vindegårdsvej 1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4632</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2216228</t>
+          <t xml:space="preserve">8940960</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H37">
-        <v>259</v>
+        <v>305</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2436,26 +2436,26 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tigervej 20</t>
+          <t xml:space="preserve">Vindegårdsvej 1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4632</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2216228</t>
+          <t xml:space="preserve">8940960</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H38">
-        <v>259</v>
+        <v>595</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2501,26 +2501,26 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tornbjergvej 42</t>
+          <t xml:space="preserve">Vindegårdsvej 1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">4623</t>
+          <t xml:space="preserve">4632</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2211891</t>
+          <t xml:space="preserve">8940960</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H39">
-        <v>583</v>
+        <v>637</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2566,26 +2566,26 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Stadion 4</t>
+          <t xml:space="preserve">Vindegårdsvej 1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4632</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">8314857</t>
+          <t xml:space="preserve">8940960</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H40">
-        <v>387</v>
+        <v>699</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Stadion 4</t>
+          <t xml:space="preserve">Ølbyvej 50</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2641,16 +2641,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">8314857</t>
+          <t xml:space="preserve">5301218</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H41">
-        <v>1222</v>
+        <v>891</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Stadion 4</t>
+          <t xml:space="preserve">Ølsemagle Kirkevej 60</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2706,16 +2706,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">8314857</t>
+          <t xml:space="preserve">2220022</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H42">
-        <v>271</v>
+        <v>299</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2761,26 +2761,26 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vindegårdsvej 1</t>
+          <t xml:space="preserve">Ølsemagle Kirkevej 62A</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">4632</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940960</t>
+          <t xml:space="preserve">8314712</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H43">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2826,45 +2826,45 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vindegårdsvej 1</t>
+          <t xml:space="preserve">Bådehavnen 8</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">4632</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940960</t>
+          <t xml:space="preserve">718862, 5300213</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H44">
-        <v>595</v>
+        <v>300</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200000890</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rådgivende ingeniørfirma</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2014-04-22</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -2891,45 +2891,45 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vindegårdsvej 1</t>
+          <t xml:space="preserve">Højelsevej 1B</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">4632</t>
+          <t xml:space="preserve">4623</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940960</t>
+          <t xml:space="preserve">718875, 2214316</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H45">
-        <v>637</v>
+        <v>2158</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">310015406</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2022-11-29</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -2956,45 +2956,45 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vindegårdsvej 1</t>
+          <t xml:space="preserve">Ravnsborgvej 3</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">4632</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940960</t>
+          <t xml:space="preserve">718829, 2594250</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H46">
-        <v>699</v>
+        <v>3072</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">310023399</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-02-04</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3021,45 +3021,45 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ølbyvej 50</t>
+          <t xml:space="preserve">Vordingborgvej 124D</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4681</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">5301218</t>
+          <t xml:space="preserve">718877, 2595511</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H47">
-        <v>891</v>
+        <v>3030</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">310023400</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-02-04</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ølsemagle Kirkevej 60</t>
+          <t xml:space="preserve">Ølbycenter 64</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2220022</t>
+          <t xml:space="preserve">269957, 269958</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3105,26 +3105,26 @@
         </is>
       </c>
       <c r="H48">
-        <v>299</v>
+        <v>2042</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311067567</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2024-08-08</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ølsemagle Kirkevej 62A</t>
+          <t xml:space="preserve">Ølbycenter 77B</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">8314712</t>
+          <t xml:space="preserve">9517472</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3170,26 +3170,26 @@
         </is>
       </c>
       <c r="H49">
-        <v>285</v>
+        <v>3416</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311067575</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2024-08-08</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bådehavnen 8</t>
+          <t xml:space="preserve">Ølbycenter 86</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3226,30 +3226,30 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">718862, 5300213</t>
+          <t xml:space="preserve">9517473</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H50">
-        <v>300</v>
+        <v>3416</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">200000890</t>
+          <t xml:space="preserve">311067568</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådgivende ingeniørfirma</t>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2014-04-22</t>
+          <t xml:space="preserve">2024-08-08</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3281,40 +3281,40 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højelsevej 1B</t>
+          <t xml:space="preserve">Slimmingevej 94</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">4623</t>
+          <t xml:space="preserve">4100</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">718875, 2214316</t>
+          <t xml:space="preserve">2592022</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H51">
-        <v>2158</v>
+        <v>699</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">310015406</t>
+          <t xml:space="preserve">311165256</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve">Topdahl ApS</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-11-29</t>
+          <t xml:space="preserve">2026-03-17</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3346,40 +3346,40 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnsborgvej 3</t>
+          <t xml:space="preserve">Slimmingevej 94</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4100</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">718829, 2594250</t>
+          <t xml:space="preserve">2592022</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H52">
-        <v>3072</v>
+        <v>264</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">310023399</t>
+          <t xml:space="preserve">311165256</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve">Topdahl ApS</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-02-04</t>
+          <t xml:space="preserve">2026-03-17</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3411,50 +3411,50 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vordingborgvej 124D</t>
+          <t xml:space="preserve">Bådehavnen 7A</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">4681</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">718877, 2595511</t>
+          <t xml:space="preserve">718841, 5300199</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="H53">
-        <v>3030</v>
+        <v>393</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">310023400</t>
+          <t xml:space="preserve">311228167</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve">Promana A/S</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-02-04</t>
+          <t xml:space="preserve">2027-02-13</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ølbycenter 64</t>
+          <t xml:space="preserve">Baneledet 1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3486,40 +3486,40 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">269957, 269958</t>
+          <t xml:space="preserve">5302948</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H54">
-        <v>2042</v>
+        <v>642</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311067567</t>
+          <t xml:space="preserve">311408662</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve">Just A/S Rådgivende Ingeniørfirma</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-08-08</t>
+          <t xml:space="preserve">2029-11-13</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3541,17 +3541,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ølbycenter 77B</t>
+          <t xml:space="preserve">Havebo 2</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4681</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">9517472</t>
+          <t xml:space="preserve">2596007</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3560,31 +3560,31 @@
         </is>
       </c>
       <c r="H55">
-        <v>3416</v>
+        <v>252</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311067575</t>
+          <t xml:space="preserve">311461664</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve">EWII Energi A/S</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-08-08</t>
+          <t xml:space="preserve">2030-09-17</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3606,17 +3606,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ølbycenter 86</t>
+          <t xml:space="preserve">Lundegårdsvej 2</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4100</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">9517473</t>
+          <t xml:space="preserve">2591592</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3625,31 +3625,31 @@
         </is>
       </c>
       <c r="H56">
-        <v>3416</v>
+        <v>1453</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311067568</t>
+          <t xml:space="preserve">311461620</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve">EWII Energi A/S</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-08-08</t>
+          <t xml:space="preserve">2030-09-17</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slimmingevej 94</t>
+          <t xml:space="preserve">Lundegårdsvej 2</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3681,40 +3681,40 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2592022</t>
+          <t xml:space="preserve">2591592</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H57">
-        <v>699</v>
+        <v>628</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311165257</t>
+          <t xml:space="preserve">311461620</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl ApS</t>
+          <t xml:space="preserve">EWII Energi A/S</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-17</t>
+          <t xml:space="preserve">2030-09-17</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3736,50 +3736,50 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slimmingevej 94</t>
+          <t xml:space="preserve">Pedersvej 100</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">4100</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2592022</t>
+          <t xml:space="preserve">5299989</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H58">
-        <v>264</v>
+        <v>1278</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311165259</t>
+          <t xml:space="preserve">311461719</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl ApS</t>
+          <t xml:space="preserve">EWII Energi A/S</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-17</t>
+          <t xml:space="preserve">2030-09-17</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3801,40 +3801,40 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bådehavnen 7A</t>
+          <t xml:space="preserve">Ejbovej 2</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4632</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">718841, 5300199</t>
+          <t xml:space="preserve">100000634</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H59">
-        <v>393</v>
+        <v>840</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311228167</t>
+          <t xml:space="preserve">311461926</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Promana A/S</t>
+          <t xml:space="preserve">EWII Energi A/S</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-13</t>
+          <t xml:space="preserve">2030-09-18</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baneledet 1</t>
+          <t xml:space="preserve">Rishøjvej 1B</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3876,30 +3876,30 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">5302948</t>
+          <t xml:space="preserve">2219478</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H60">
-        <v>642</v>
+        <v>383</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311408662</t>
+          <t xml:space="preserve">311461925</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Just A/S Rådgivende Ingeniørfirma</t>
+          <t xml:space="preserve">EWII Energi A/S</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-13</t>
+          <t xml:space="preserve">2030-09-18</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -3931,17 +3931,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havebo 2</t>
+          <t xml:space="preserve">Rishøjvej 3</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">4681</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2596007</t>
+          <t xml:space="preserve">2219384</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3950,11 +3950,11 @@
         </is>
       </c>
       <c r="H61">
-        <v>252</v>
+        <v>367</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311461664</t>
+          <t xml:space="preserve">311462237</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-17</t>
+          <t xml:space="preserve">2030-09-21</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -3996,30 +3996,30 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundegårdsvej 2</t>
+          <t xml:space="preserve">Pogebanken 3</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">4100</t>
+          <t xml:space="preserve">4681</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2591592</t>
+          <t xml:space="preserve">2595275</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H62">
-        <v>1453</v>
+        <v>470</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311461620</t>
+          <t xml:space="preserve">311466054</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-17</t>
+          <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4061,30 +4061,30 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundegårdsvej 2</t>
+          <t xml:space="preserve">Sankt Gertrudsstræde 30</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">4100</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2591592</t>
+          <t xml:space="preserve">5298693</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H63">
-        <v>628</v>
+        <v>325</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311461620</t>
+          <t xml:space="preserve">311468126</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-17</t>
+          <t xml:space="preserve">2030-10-20</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4126,17 +4126,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pedersvej 100</t>
+          <t xml:space="preserve">Pogebanken 7</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4681</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5299989</t>
+          <t xml:space="preserve">2595274</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4145,11 +4145,11 @@
         </is>
       </c>
       <c r="H64">
-        <v>1278</v>
+        <v>379</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311461719</t>
+          <t xml:space="preserve">311469400</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-17</t>
+          <t xml:space="preserve">2030-10-23</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4191,30 +4191,30 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejbovej 2</t>
+          <t xml:space="preserve">Tangmosevej 1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">4632</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">100000634</t>
+          <t xml:space="preserve">5299172</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H65">
-        <v>840</v>
+        <v>877</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311461926</t>
+          <t xml:space="preserve">311469402</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-18</t>
+          <t xml:space="preserve">2030-10-23</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rishøjvej 1B</t>
+          <t xml:space="preserve">Tangmosevej 1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4266,20 +4266,20 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2219478</t>
+          <t xml:space="preserve">5299172</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H66">
-        <v>383</v>
+        <v>282</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311461925</t>
+          <t xml:space="preserve">311469399</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-18</t>
+          <t xml:space="preserve">2030-10-23</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4321,17 +4321,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rishøjvej 3</t>
+          <t xml:space="preserve">Pogebanken 5</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4681</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2219384</t>
+          <t xml:space="preserve">2595275</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4340,11 +4340,11 @@
         </is>
       </c>
       <c r="H67">
-        <v>367</v>
+        <v>503</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311462237</t>
+          <t xml:space="preserve">311474129</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-21</t>
+          <t xml:space="preserve">2030-11-09</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4386,30 +4386,30 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pogebanken 3</t>
+          <t xml:space="preserve">Boholtevej 181</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">4681</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2595275</t>
+          <t xml:space="preserve">5302760</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H68">
-        <v>470</v>
+        <v>597</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466054</t>
+          <t xml:space="preserve">311474331</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-08</t>
+          <t xml:space="preserve">2030-11-10</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sankt Gertrudsstræde 30</t>
+          <t xml:space="preserve">Boholtevej 91</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298693</t>
+          <t xml:space="preserve">5302764</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4470,11 +4470,11 @@
         </is>
       </c>
       <c r="H69">
-        <v>325</v>
+        <v>1199</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311468126</t>
+          <t xml:space="preserve">311474762</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-20</t>
+          <t xml:space="preserve">2030-11-11</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4516,17 +4516,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pogebanken 7</t>
+          <t xml:space="preserve">Accisevej 1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">4681</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2595274</t>
+          <t xml:space="preserve">5299241</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4535,11 +4535,11 @@
         </is>
       </c>
       <c r="H70">
-        <v>379</v>
+        <v>734</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311469400</t>
+          <t xml:space="preserve">311475433</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-23</t>
+          <t xml:space="preserve">2030-11-13</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tangmosevej 1</t>
+          <t xml:space="preserve">Allegade 3</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">5299172</t>
+          <t xml:space="preserve">5298850</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4600,11 +4600,11 @@
         </is>
       </c>
       <c r="H71">
-        <v>877</v>
+        <v>321</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311469402</t>
+          <t xml:space="preserve">311475476</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-23</t>
+          <t xml:space="preserve">2030-11-13</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tangmosevej 1</t>
+          <t xml:space="preserve">Boholtevej 85A</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4656,20 +4656,20 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">5299172</t>
+          <t xml:space="preserve">5302763</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H72">
-        <v>282</v>
+        <v>1324</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311469399</t>
+          <t xml:space="preserve">311475438</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-23</t>
+          <t xml:space="preserve">2030-11-13</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4711,17 +4711,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pogebanken 5</t>
+          <t xml:space="preserve">Dyrlundsvej 11</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">4681</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2595275</t>
+          <t xml:space="preserve">5299044</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4730,11 +4730,11 @@
         </is>
       </c>
       <c r="H73">
-        <v>503</v>
+        <v>557</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474129</t>
+          <t xml:space="preserve">311475426</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-09</t>
+          <t xml:space="preserve">2030-11-13</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boholtevej 181</t>
+          <t xml:space="preserve">Karlemosevej 46</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">5302760</t>
+          <t xml:space="preserve">2215847</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4795,11 +4795,11 @@
         </is>
       </c>
       <c r="H74">
-        <v>597</v>
+        <v>552</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474331</t>
+          <t xml:space="preserve">311475459</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-10</t>
+          <t xml:space="preserve">2030-11-13</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boholtevej 91</t>
+          <t xml:space="preserve">Lerbæk Torv 5</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">5302764</t>
+          <t xml:space="preserve">2593903</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4860,11 +4860,11 @@
         </is>
       </c>
       <c r="H75">
-        <v>1199</v>
+        <v>722</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474762</t>
+          <t xml:space="preserve">311475469</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-11</t>
+          <t xml:space="preserve">2030-11-13</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -4906,17 +4906,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accisevej 1</t>
+          <t xml:space="preserve">Østertorp 67</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4681</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">5299241</t>
+          <t xml:space="preserve">2594914</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4925,11 +4925,11 @@
         </is>
       </c>
       <c r="H76">
-        <v>734</v>
+        <v>442</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475433</t>
+          <t xml:space="preserve">311475465</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -4971,30 +4971,30 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allegade 3</t>
+          <t xml:space="preserve">Østertorp 68</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4681</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298850</t>
+          <t xml:space="preserve">2594914</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H77">
-        <v>321</v>
+        <v>502</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475476</t>
+          <t xml:space="preserve">311475465</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boholtevej 85A</t>
+          <t xml:space="preserve">Gymnasievej 22</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">5302763</t>
+          <t xml:space="preserve">8638680</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5055,11 +5055,11 @@
         </is>
       </c>
       <c r="H78">
-        <v>1324</v>
+        <v>465</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475438</t>
+          <t xml:space="preserve">311475851</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-13</t>
+          <t xml:space="preserve">2030-11-16</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyrlundsvej 11</t>
+          <t xml:space="preserve">Gymnasievej 24</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">5299044</t>
+          <t xml:space="preserve">9370842</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5120,11 +5120,11 @@
         </is>
       </c>
       <c r="H79">
-        <v>557</v>
+        <v>784</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475426</t>
+          <t xml:space="preserve">311475844</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-13</t>
+          <t xml:space="preserve">2030-11-16</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5166,17 +5166,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karlemosevej 46</t>
+          <t xml:space="preserve">Mellemmarksvej 13</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4681</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2215847</t>
+          <t xml:space="preserve">7010687</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5185,11 +5185,11 @@
         </is>
       </c>
       <c r="H80">
-        <v>552</v>
+        <v>722</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475459</t>
+          <t xml:space="preserve">311477758</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-13</t>
+          <t xml:space="preserve">2030-11-23</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerbæk Torv 5</t>
+          <t xml:space="preserve">Slagterivej 12</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2593903</t>
+          <t xml:space="preserve">5299224</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -5250,11 +5250,11 @@
         </is>
       </c>
       <c r="H81">
-        <v>722</v>
+        <v>1608</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475469</t>
+          <t xml:space="preserve">311483210</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-13</t>
+          <t xml:space="preserve">2030-12-16</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5296,17 +5296,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østertorp 67</t>
+          <t xml:space="preserve">Byvej 31</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">4681</t>
+          <t xml:space="preserve">4682</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2594914</t>
+          <t xml:space="preserve">2597534</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -5315,11 +5315,11 @@
         </is>
       </c>
       <c r="H82">
-        <v>442</v>
+        <v>600</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475465</t>
+          <t xml:space="preserve">311483621</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-13</t>
+          <t xml:space="preserve">2030-12-17</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5361,17 +5361,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østertorp 68</t>
+          <t xml:space="preserve">Byvej 31</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">4681</t>
+          <t xml:space="preserve">4682</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2594914</t>
+          <t xml:space="preserve">2597534</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -5380,11 +5380,11 @@
         </is>
       </c>
       <c r="H83">
-        <v>502</v>
+        <v>948</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475465</t>
+          <t xml:space="preserve">311483621</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-13</t>
+          <t xml:space="preserve">2030-12-17</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5426,17 +5426,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gymnasievej 22</t>
+          <t xml:space="preserve">Parkvej 8</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4140</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">8638680</t>
+          <t xml:space="preserve">2210082</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5445,11 +5445,11 @@
         </is>
       </c>
       <c r="H84">
-        <v>465</v>
+        <v>514</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475851</t>
+          <t xml:space="preserve">311483562</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-16</t>
+          <t xml:space="preserve">2030-12-17</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gymnasievej 24</t>
+          <t xml:space="preserve">Høgevej 9</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5501,20 +5501,20 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">9370842</t>
+          <t xml:space="preserve">9168077</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H85">
-        <v>784</v>
+        <v>530</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475844</t>
+          <t xml:space="preserve">311483961</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-16</t>
+          <t xml:space="preserve">2030-12-18</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5556,30 +5556,30 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mellemmarksvej 13</t>
+          <t xml:space="preserve">Høgevej 9</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">4681</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">7010687</t>
+          <t xml:space="preserve">9168077</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H86">
-        <v>722</v>
+        <v>1128</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311477758</t>
+          <t xml:space="preserve">311483963</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-23</t>
+          <t xml:space="preserve">2030-12-18</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slagterivej 12</t>
+          <t xml:space="preserve">Ørnevej 11</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5631,20 +5631,20 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">5299224</t>
+          <t xml:space="preserve">9168077</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H87">
-        <v>1608</v>
+        <v>1356</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483210</t>
+          <t xml:space="preserve">311483967</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-16</t>
+          <t xml:space="preserve">2030-12-18</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5686,30 +5686,30 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 31</t>
+          <t xml:space="preserve">Ørnevej 15</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">4682</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2597534</t>
+          <t xml:space="preserve">9168077</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H88">
-        <v>600</v>
+        <v>885</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483621</t>
+          <t xml:space="preserve">311483967</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-17</t>
+          <t xml:space="preserve">2030-12-18</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5751,30 +5751,30 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 31</t>
+          <t xml:space="preserve">Aldersro 3</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">4682</t>
+          <t xml:space="preserve">4681</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2597534</t>
+          <t xml:space="preserve">10175791</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H89">
-        <v>948</v>
+        <v>354</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483621</t>
+          <t xml:space="preserve">311484259</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-17</t>
+          <t xml:space="preserve">2030-12-21</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -5816,40 +5816,40 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 8</t>
+          <t xml:space="preserve">Aldersro 3</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">4140</t>
+          <t xml:space="preserve">4681</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2210082</t>
+          <t xml:space="preserve">10175791</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H90">
-        <v>514</v>
+        <v>428</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483562</t>
+          <t xml:space="preserve">311484263</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t xml:space="preserve">EWII Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-17</t>
+          <t xml:space="preserve">2030-12-21</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -5881,30 +5881,30 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høgevej 9</t>
+          <t xml:space="preserve">Byvej 33</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4682</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">9168077</t>
+          <t xml:space="preserve">2597534</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H91">
-        <v>530</v>
+        <v>437</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483961</t>
+          <t xml:space="preserve">311484253</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5914,7 +5914,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-18</t>
+          <t xml:space="preserve">2030-12-21</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -5946,30 +5946,30 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høgevej 9</t>
+          <t xml:space="preserve">Parkvej 13</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4140</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">9168077</t>
+          <t xml:space="preserve">2209985</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H92">
-        <v>1128</v>
+        <v>1171</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483963</t>
+          <t xml:space="preserve">311484281</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-18</t>
+          <t xml:space="preserve">2030-12-21</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørnevej 11</t>
+          <t xml:space="preserve">Tigervej 20</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6021,20 +6021,20 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">9168077</t>
+          <t xml:space="preserve">2216228</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H93">
-        <v>1356</v>
+        <v>504</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483967</t>
+          <t xml:space="preserve">311489560</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6044,7 +6044,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-18</t>
+          <t xml:space="preserve">2031-01-22</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørnevej 15</t>
+          <t xml:space="preserve">Frihedsvej 12</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6086,20 +6086,20 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">9168077</t>
+          <t xml:space="preserve">5300128</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H94">
-        <v>885</v>
+        <v>803</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483967</t>
+          <t xml:space="preserve">311491356</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-18</t>
+          <t xml:space="preserve">2031-01-29</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aldersro 3</t>
+          <t xml:space="preserve">Søndre Centervej 112</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">4681</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">10175791</t>
+          <t xml:space="preserve">7562165</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -6160,11 +6160,11 @@
         </is>
       </c>
       <c r="H95">
-        <v>354</v>
+        <v>524</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311484259</t>
+          <t xml:space="preserve">311491358</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-21</t>
+          <t xml:space="preserve">2031-01-29</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6206,40 +6206,40 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aldersro 3</t>
+          <t xml:space="preserve">Højelsevej 1A</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">4681</t>
+          <t xml:space="preserve">4623</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">10175791</t>
+          <t xml:space="preserve">2214316</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H96">
-        <v>428</v>
+        <v>266</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311484263</t>
+          <t xml:space="preserve">311493260</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">EWII Energi A/S</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-21</t>
+          <t xml:space="preserve">2031-02-05</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6271,30 +6271,30 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 33</t>
+          <t xml:space="preserve">Rishøjvej 5</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">4682</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2597534</t>
+          <t xml:space="preserve">2219479</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H97">
-        <v>437</v>
+        <v>689</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311484253</t>
+          <t xml:space="preserve">311493605</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-21</t>
+          <t xml:space="preserve">2031-02-08</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6336,17 +6336,17 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 13</t>
+          <t xml:space="preserve">Ved Stadion 6</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">4140</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209985</t>
+          <t xml:space="preserve">100298242, 100298243</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -6355,21 +6355,21 @@
         </is>
       </c>
       <c r="H98">
-        <v>1171</v>
+        <v>2442</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311484281</t>
+          <t xml:space="preserve">311500199</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t xml:space="preserve">EWII Energi A/S</t>
+          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-21</t>
+          <t xml:space="preserve">2031-03-03</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6401,17 +6401,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tigervej 20</t>
+          <t xml:space="preserve">Vordingborgvej 124C</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4681</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2216228</t>
+          <t xml:space="preserve">2595487</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -6420,11 +6420,11 @@
         </is>
       </c>
       <c r="H99">
-        <v>504</v>
+        <v>873</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311489560</t>
+          <t xml:space="preserve">311504181</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-22</t>
+          <t xml:space="preserve">2031-03-17</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6466,30 +6466,30 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frihedsvej 12</t>
+          <t xml:space="preserve">Vordingborgvej 124E</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4681</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">5300128</t>
+          <t xml:space="preserve">2595646</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H100">
-        <v>803</v>
+        <v>1660</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311491356</t>
+          <t xml:space="preserve">311504185</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6499,7 +6499,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-29</t>
+          <t xml:space="preserve">2031-03-17</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6531,40 +6531,40 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Centervej 112</t>
+          <t xml:space="preserve">Halvejen 14</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4632</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">7562165</t>
+          <t xml:space="preserve">2589978</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H101">
-        <v>524</v>
+        <v>580</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311491358</t>
+          <t xml:space="preserve">311510337</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t xml:space="preserve">EWII Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-29</t>
+          <t xml:space="preserve">2031-04-07</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6596,40 +6596,40 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højelsevej 1A</t>
+          <t xml:space="preserve">Halvejen 4</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">4623</t>
+          <t xml:space="preserve">4632</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2214316</t>
+          <t xml:space="preserve">2589978</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H102">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311493260</t>
+          <t xml:space="preserve">311510337</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t xml:space="preserve">EWII Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-05</t>
+          <t xml:space="preserve">2031-04-07</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rishøjvej 5</t>
+          <t xml:space="preserve">Slimmingevej 78</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4100</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2219479</t>
+          <t xml:space="preserve">2591660</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6680,11 +6680,11 @@
         </is>
       </c>
       <c r="H103">
-        <v>689</v>
+        <v>313</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311493605</t>
+          <t xml:space="preserve">311510335</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-08</t>
+          <t xml:space="preserve">2031-04-07</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6726,40 +6726,40 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Stadion 6</t>
+          <t xml:space="preserve">Møllevej 4</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4140</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">100298242, 100298243</t>
+          <t xml:space="preserve">2209946</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H104">
-        <v>2442</v>
+        <v>286</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311500199</t>
+          <t xml:space="preserve">311512262</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-03</t>
+          <t xml:space="preserve">2031-04-14</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6791,30 +6791,30 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vordingborgvej 124C</t>
+          <t xml:space="preserve">Møllevej 11C</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">4681</t>
+          <t xml:space="preserve">4140</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2595487</t>
+          <t xml:space="preserve">100039640</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H105">
-        <v>873</v>
+        <v>1189</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311504181</t>
+          <t xml:space="preserve">311512586</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-17</t>
+          <t xml:space="preserve">2031-04-15</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -6856,30 +6856,30 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vordingborgvej 124E</t>
+          <t xml:space="preserve">Ahornvej 1B</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">4681</t>
+          <t xml:space="preserve">4632</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2595646</t>
+          <t xml:space="preserve">2591270</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H106">
-        <v>1660</v>
+        <v>380</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311504185</t>
+          <t xml:space="preserve">311513452</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-17</t>
+          <t xml:space="preserve">2031-04-19</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halvejen 14</t>
+          <t xml:space="preserve">Gartnervej 18</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6931,30 +6931,30 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2589978</t>
+          <t xml:space="preserve">8352544</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H107">
-        <v>580</v>
+        <v>485</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311510337</t>
+          <t xml:space="preserve">311513468</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">EWII Energi A/S</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-07</t>
+          <t xml:space="preserve">2031-04-19</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -6986,40 +6986,40 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halvejen 4</t>
+          <t xml:space="preserve">Marksvinget 22</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">4632</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2589978</t>
+          <t xml:space="preserve">5302628</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H108">
-        <v>252</v>
+        <v>453</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311510337</t>
+          <t xml:space="preserve">311513379</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">EWII Energi A/S</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-07</t>
+          <t xml:space="preserve">2031-04-19</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7051,17 +7051,17 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slimmingevej 78</t>
+          <t xml:space="preserve">Rønnevej 21</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">4100</t>
+          <t xml:space="preserve">4140</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2591660</t>
+          <t xml:space="preserve">2209908</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -7070,11 +7070,11 @@
         </is>
       </c>
       <c r="H109">
-        <v>313</v>
+        <v>422</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311510336</t>
+          <t xml:space="preserve">311513456</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-07</t>
+          <t xml:space="preserve">2031-04-19</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -7116,40 +7116,40 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevej 4</t>
+          <t xml:space="preserve">Kirkepladsen 2</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">4140</t>
+          <t xml:space="preserve">4681</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209946</t>
+          <t xml:space="preserve">2594623</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H110">
-        <v>286</v>
+        <v>416</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311512262</t>
+          <t xml:space="preserve">311514520</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">EWII Energi A/S</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-14</t>
+          <t xml:space="preserve">2031-04-22</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7181,30 +7181,30 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevej 11C</t>
+          <t xml:space="preserve">Scheelsvej 2A</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">4140</t>
+          <t xml:space="preserve">4681</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">100039640</t>
+          <t xml:space="preserve">2595960</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H111">
-        <v>1189</v>
+        <v>1279</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311512586</t>
+          <t xml:space="preserve">311517451</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-15</t>
+          <t xml:space="preserve">2031-05-04</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7246,30 +7246,30 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ahornvej 1B</t>
+          <t xml:space="preserve">Skovvang 3</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">4632</t>
+          <t xml:space="preserve">4623</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2591270</t>
+          <t xml:space="preserve">8940846</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H112">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311513452</t>
+          <t xml:space="preserve">311517474</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7279,7 +7279,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-19</t>
+          <t xml:space="preserve">2031-05-04</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7311,17 +7311,17 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gartnervej 18</t>
+          <t xml:space="preserve">Boholtevej 89</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">4632</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">8352544</t>
+          <t xml:space="preserve">5302765</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -7330,11 +7330,11 @@
         </is>
       </c>
       <c r="H113">
-        <v>485</v>
+        <v>455</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311513468</t>
+          <t xml:space="preserve">311519300</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-19</t>
+          <t xml:space="preserve">2031-05-11</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marksvinget 22</t>
+          <t xml:space="preserve">Egøjevej 72</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">5302628</t>
+          <t xml:space="preserve">5301648</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -7395,11 +7395,11 @@
         </is>
       </c>
       <c r="H114">
-        <v>453</v>
+        <v>480</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311513379</t>
+          <t xml:space="preserve">311519301</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-19</t>
+          <t xml:space="preserve">2031-05-11</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7441,17 +7441,17 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rønnevej 21</t>
+          <t xml:space="preserve">Ravnsborgvej 12</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">4140</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209908</t>
+          <t xml:space="preserve">8038405</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -7460,11 +7460,11 @@
         </is>
       </c>
       <c r="H115">
-        <v>422</v>
+        <v>544</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311513456</t>
+          <t xml:space="preserve">311519303</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-19</t>
+          <t xml:space="preserve">2031-05-11</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7506,17 +7506,17 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkepladsen 2</t>
+          <t xml:space="preserve">Ravnsborgvej 14</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">4681</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2594623</t>
+          <t xml:space="preserve">8239899</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -7525,11 +7525,11 @@
         </is>
       </c>
       <c r="H116">
-        <v>416</v>
+        <v>611</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311514520</t>
+          <t xml:space="preserve">311519304</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-22</t>
+          <t xml:space="preserve">2031-05-11</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7571,17 +7571,17 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheelsvej 2A</t>
+          <t xml:space="preserve">Vollerslevvej 12</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">4681</t>
+          <t xml:space="preserve">4632</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2595960</t>
+          <t xml:space="preserve">7609591</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -7590,11 +7590,11 @@
         </is>
       </c>
       <c r="H117">
-        <v>1279</v>
+        <v>285</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311517451</t>
+          <t xml:space="preserve">311519591</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-04</t>
+          <t xml:space="preserve">2031-05-11</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7636,30 +7636,30 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvang 3</t>
+          <t xml:space="preserve">Hovedgaden 65</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">4623</t>
+          <t xml:space="preserve">4140</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940846</t>
+          <t xml:space="preserve">265067, 265068</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H118">
-        <v>400</v>
+        <v>2578</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311517474</t>
+          <t xml:space="preserve">311519776</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7669,7 +7669,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-04</t>
+          <t xml:space="preserve">2031-05-12</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7701,17 +7701,17 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boholtevej 89</t>
+          <t xml:space="preserve">Parkvej 2</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4140</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">5302765</t>
+          <t xml:space="preserve">2209991</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -7720,11 +7720,11 @@
         </is>
       </c>
       <c r="H119">
-        <v>455</v>
+        <v>520</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311519300</t>
+          <t xml:space="preserve">311521608</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-11</t>
+          <t xml:space="preserve">2031-05-20</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egøjevej 72</t>
+          <t xml:space="preserve">Søndre Badevej 1</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7776,20 +7776,20 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">5301648</t>
+          <t xml:space="preserve">5300240</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H120">
-        <v>480</v>
+        <v>1275</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311519301</t>
+          <t xml:space="preserve">311527885</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7799,7 +7799,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-11</t>
+          <t xml:space="preserve">2031-06-14</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7831,17 +7831,17 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnsborgvej 12</t>
+          <t xml:space="preserve">Baunebjergvej 1C</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4623</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">8038405</t>
+          <t xml:space="preserve">2214307</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -7850,11 +7850,11 @@
         </is>
       </c>
       <c r="H121">
-        <v>544</v>
+        <v>2884</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311519303</t>
+          <t xml:space="preserve">311533128</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-11</t>
+          <t xml:space="preserve">2031-07-02</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -7896,30 +7896,30 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnsborgvej 14</t>
+          <t xml:space="preserve">Baunebjergvej 1C</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4623</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">8239899</t>
+          <t xml:space="preserve">2214307</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H122">
-        <v>611</v>
+        <v>972</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311519304</t>
+          <t xml:space="preserve">311533129</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-11</t>
+          <t xml:space="preserve">2031-07-02</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -7961,30 +7961,30 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vollerslevvej 12</t>
+          <t xml:space="preserve">Lerbæk Torv 11</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">4632</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">7609591</t>
+          <t xml:space="preserve">2593904</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H123">
-        <v>285</v>
+        <v>704</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311519591</t>
+          <t xml:space="preserve">311533127</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-11</t>
+          <t xml:space="preserve">2031-07-02</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -8026,17 +8026,17 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 65</t>
+          <t xml:space="preserve">Lerbæk Torv 12</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">4140</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">265067, 265068</t>
+          <t xml:space="preserve">268651</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -8045,11 +8045,11 @@
         </is>
       </c>
       <c r="H124">
-        <v>2578</v>
+        <v>602</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311519776</t>
+          <t xml:space="preserve">311533123</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -8059,7 +8059,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-12</t>
+          <t xml:space="preserve">2031-07-02</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -8091,30 +8091,30 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 2</t>
+          <t xml:space="preserve">Lerbæk Torv 2</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">4140</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209991</t>
+          <t xml:space="preserve">268652, 268653</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H125">
-        <v>520</v>
+        <v>2677</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311521608</t>
+          <t xml:space="preserve">311533125</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -8124,7 +8124,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-20</t>
+          <t xml:space="preserve">2031-07-02</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Badevej 1</t>
+          <t xml:space="preserve">Nørre Boulevard 101</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8166,20 +8166,20 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">5300240</t>
+          <t xml:space="preserve">5300077</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H126">
-        <v>1275</v>
+        <v>1158</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311527885</t>
+          <t xml:space="preserve">311533130</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-14</t>
+          <t xml:space="preserve">2031-07-02</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8221,17 +8221,17 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunebjergvej 1C</t>
+          <t xml:space="preserve">Nørre Boulevard 103</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">4623</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2214307</t>
+          <t xml:space="preserve">5300077</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -8240,11 +8240,11 @@
         </is>
       </c>
       <c r="H127">
-        <v>2884</v>
+        <v>2139</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533128</t>
+          <t xml:space="preserve">311533130</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunebjergvej 1C</t>
+          <t xml:space="preserve">Fogedvej 4</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8296,20 +8296,20 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2214307</t>
+          <t xml:space="preserve">8738812</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H128">
-        <v>972</v>
+        <v>511</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533129</t>
+          <t xml:space="preserve">311533507</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -8319,7 +8319,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-02</t>
+          <t xml:space="preserve">2031-07-05</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8351,30 +8351,30 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerbæk Torv 11</t>
+          <t xml:space="preserve">Gemsevej 23</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4623</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2593904</t>
+          <t xml:space="preserve">8127101</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H129">
-        <v>704</v>
+        <v>557</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533127</t>
+          <t xml:space="preserve">311533512</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-02</t>
+          <t xml:space="preserve">2031-07-05</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8416,17 +8416,17 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerbæk Torv 12</t>
+          <t xml:space="preserve">Gemsevej 25</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4623</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">268651</t>
+          <t xml:space="preserve">2212560</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -8435,11 +8435,11 @@
         </is>
       </c>
       <c r="H130">
-        <v>602</v>
+        <v>403</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533123</t>
+          <t xml:space="preserve">311533516</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-02</t>
+          <t xml:space="preserve">2031-07-05</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerbæk Torv 2</t>
+          <t xml:space="preserve">Klemmenstrupvej 31</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8491,20 +8491,20 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">268652, 268653</t>
+          <t xml:space="preserve">7382834</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H131">
-        <v>2677</v>
+        <v>1002</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533125</t>
+          <t xml:space="preserve">311533492</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-02</t>
+          <t xml:space="preserve">2031-07-05</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørre Boulevard 101</t>
+          <t xml:space="preserve">Langelandsvej 70</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8556,20 +8556,20 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">5300077</t>
+          <t xml:space="preserve">2593898</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H132">
-        <v>1158</v>
+        <v>5774</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533130</t>
+          <t xml:space="preserve">311533502</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-02</t>
+          <t xml:space="preserve">2031-07-05</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørre Boulevard 103</t>
+          <t xml:space="preserve">Langelandsvej 72</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8621,20 +8621,20 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">5300077</t>
+          <t xml:space="preserve">2593898</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H133">
-        <v>2139</v>
+        <v>544</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533130</t>
+          <t xml:space="preserve">311533496</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-02</t>
+          <t xml:space="preserve">2031-07-05</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8676,17 +8676,17 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fogedvej 4</t>
+          <t xml:space="preserve">Pogebanken 9</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">4623</t>
+          <t xml:space="preserve">4681</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">8738812</t>
+          <t xml:space="preserve">8314790</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -8695,11 +8695,11 @@
         </is>
       </c>
       <c r="H134">
-        <v>511</v>
+        <v>5811</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533507</t>
+          <t xml:space="preserve">311533528</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -8741,17 +8741,17 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gemsevej 23</t>
+          <t xml:space="preserve">Pogebanken 16</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">4623</t>
+          <t xml:space="preserve">4681</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">8127101</t>
+          <t xml:space="preserve">2595280</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -8760,11 +8760,11 @@
         </is>
       </c>
       <c r="H135">
-        <v>557</v>
+        <v>996</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533512</t>
+          <t xml:space="preserve">311538975</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-05</t>
+          <t xml:space="preserve">2031-08-04</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8806,17 +8806,17 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gemsevej 25</t>
+          <t xml:space="preserve">Vedskøllevej 1A</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">4623</t>
+          <t xml:space="preserve">4681</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2212560</t>
+          <t xml:space="preserve">8314762</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -8825,11 +8825,11 @@
         </is>
       </c>
       <c r="H136">
-        <v>403</v>
+        <v>1551</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533516</t>
+          <t xml:space="preserve">311538960</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -8839,7 +8839,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-05</t>
+          <t xml:space="preserve">2031-08-04</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8871,30 +8871,30 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klemmenstrupvej 31</t>
+          <t xml:space="preserve">Vedskøllevej 1A</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4681</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">7382834</t>
+          <t xml:space="preserve">8314762</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H137">
-        <v>1002</v>
+        <v>4950</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533492</t>
+          <t xml:space="preserve">311538960</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-05</t>
+          <t xml:space="preserve">2031-08-04</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -8936,30 +8936,30 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langelandsvej 70</t>
+          <t xml:space="preserve">Vedskøllevej 1A</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4681</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2593898</t>
+          <t xml:space="preserve">8314762</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H138">
-        <v>5774</v>
+        <v>906</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533502</t>
+          <t xml:space="preserve">311538960</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -8969,7 +8969,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-05</t>
+          <t xml:space="preserve">2031-08-04</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langelandsvej 72</t>
+          <t xml:space="preserve">Ølbycenter 51</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -9011,20 +9011,20 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2593898</t>
+          <t xml:space="preserve">2215752</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H139">
-        <v>544</v>
+        <v>2429</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533496</t>
+          <t xml:space="preserve">311538964</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-05</t>
+          <t xml:space="preserve">2031-08-04</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -9066,17 +9066,17 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pogebanken 9</t>
+          <t xml:space="preserve">Ølbyvej 50</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve">4681</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">8314790</t>
+          <t xml:space="preserve">5301218</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -9085,11 +9085,11 @@
         </is>
       </c>
       <c r="H140">
-        <v>5811</v>
+        <v>3420</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533528</t>
+          <t xml:space="preserve">311538952</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -9099,7 +9099,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-05</t>
+          <t xml:space="preserve">2031-08-04</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -9131,7 +9131,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pogebanken 16</t>
+          <t xml:space="preserve">Billesborgvej 1</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2595280</t>
+          <t xml:space="preserve">2595904</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -9150,21 +9150,21 @@
         </is>
       </c>
       <c r="H141">
-        <v>996</v>
+        <v>7177</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311538975</t>
+          <t xml:space="preserve">311539435</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t xml:space="preserve">EWII Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-04</t>
+          <t xml:space="preserve">2031-08-06</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -9196,7 +9196,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vedskøllevej 1A</t>
+          <t xml:space="preserve">Billesborgvej 1B</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -9206,30 +9206,30 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">8314762</t>
+          <t xml:space="preserve">2595904</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H142">
-        <v>1551</v>
+        <v>650</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311538960</t>
+          <t xml:space="preserve">311539435</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t xml:space="preserve">EWII Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-04</t>
+          <t xml:space="preserve">2031-08-06</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -9261,30 +9261,30 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vedskøllevej 1A</t>
+          <t xml:space="preserve">Hovedgaden 39</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">4681</t>
+          <t xml:space="preserve">4140</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">8314762</t>
+          <t xml:space="preserve">2209661</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H143">
-        <v>4950</v>
+        <v>2435</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311538960</t>
+          <t xml:space="preserve">311539849</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -9294,7 +9294,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-04</t>
+          <t xml:space="preserve">2031-08-10</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -9326,30 +9326,30 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vedskøllevej 1A</t>
+          <t xml:space="preserve">Hovedgaden 39</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">4681</t>
+          <t xml:space="preserve">4140</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">8314762</t>
+          <t xml:space="preserve">2209661</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H144">
-        <v>906</v>
+        <v>720</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311538960</t>
+          <t xml:space="preserve">311539849</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-04</t>
+          <t xml:space="preserve">2031-08-10</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -9391,30 +9391,30 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ølbycenter 51</t>
+          <t xml:space="preserve">Hovedgaden 39</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4140</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2215752</t>
+          <t xml:space="preserve">2209661</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H145">
-        <v>2429</v>
+        <v>1218</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311538964</t>
+          <t xml:space="preserve">311539849</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -9424,7 +9424,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-04</t>
+          <t xml:space="preserve">2031-08-10</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -9456,30 +9456,30 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ølbyvej 50</t>
+          <t xml:space="preserve">Hovedgaden 39</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4140</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">5301218</t>
+          <t xml:space="preserve">2209661</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H146">
-        <v>3420</v>
+        <v>1187</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311538952</t>
+          <t xml:space="preserve">311539849</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -9489,7 +9489,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-04</t>
+          <t xml:space="preserve">2031-08-10</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -9521,40 +9521,40 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billesborgvej 1</t>
+          <t xml:space="preserve">Hovedgaden 39</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">4681</t>
+          <t xml:space="preserve">4140</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2595904</t>
+          <t xml:space="preserve">2209661</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H147">
-        <v>7177</v>
+        <v>1590</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539435</t>
+          <t xml:space="preserve">311539849</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">EWII Energi A/S</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-06</t>
+          <t xml:space="preserve">2031-08-10</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -9586,40 +9586,40 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billesborgvej 1B</t>
+          <t xml:space="preserve">Hovedgaden 39</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">4681</t>
+          <t xml:space="preserve">4140</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2595904</t>
+          <t xml:space="preserve">2209661</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H148">
-        <v>650</v>
+        <v>3575</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539435</t>
+          <t xml:space="preserve">311539849</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">EWII Energi A/S</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-06</t>
+          <t xml:space="preserve">2031-08-10</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -9651,30 +9651,30 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 39</t>
+          <t xml:space="preserve">Kirkestræde 22</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve">4140</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209661</t>
+          <t xml:space="preserve">8948780</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H149">
-        <v>2435</v>
+        <v>980</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539849</t>
+          <t xml:space="preserve">311540512</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -9684,7 +9684,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-10</t>
+          <t xml:space="preserve">2031-08-12</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -9716,30 +9716,30 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 39</t>
+          <t xml:space="preserve">Kirkestræde 24</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">4140</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209661</t>
+          <t xml:space="preserve">8948780</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H150">
-        <v>720</v>
+        <v>253</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539849</t>
+          <t xml:space="preserve">311540512</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-10</t>
+          <t xml:space="preserve">2031-08-12</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -9781,30 +9781,30 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 39</t>
+          <t xml:space="preserve">Gemsevej 19</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">4140</t>
+          <t xml:space="preserve">4623</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209661</t>
+          <t xml:space="preserve">2212648</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H151">
-        <v>1218</v>
+        <v>443</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539849</t>
+          <t xml:space="preserve">311540701</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-10</t>
+          <t xml:space="preserve">2031-08-13</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -9846,30 +9846,30 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 39</t>
+          <t xml:space="preserve">Gymnasievej 8</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve">4140</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209661</t>
+          <t xml:space="preserve">100040993</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H152">
-        <v>1187</v>
+        <v>756</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539849</t>
+          <t xml:space="preserve">311543562</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -9879,7 +9879,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-10</t>
+          <t xml:space="preserve">2031-08-26</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -9911,30 +9911,30 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 39</t>
+          <t xml:space="preserve">Fændediget 4</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t xml:space="preserve">4140</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209661</t>
+          <t xml:space="preserve">5299406</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H153">
-        <v>1590</v>
+        <v>481</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539849</t>
+          <t xml:space="preserve">311544545</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-10</t>
+          <t xml:space="preserve">2031-08-31</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -9976,30 +9976,30 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 39</t>
+          <t xml:space="preserve">Skovvang 6</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t xml:space="preserve">4140</t>
+          <t xml:space="preserve">4623</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209661</t>
+          <t xml:space="preserve">8940846</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H154">
-        <v>3575</v>
+        <v>8394</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539849</t>
+          <t xml:space="preserve">311544560</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-10</t>
+          <t xml:space="preserve">2031-08-31</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -10041,30 +10041,30 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkestræde 22</t>
+          <t xml:space="preserve">Lidemarksvej 97A</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4632</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">8948780</t>
+          <t xml:space="preserve">2589978</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H155">
-        <v>980</v>
+        <v>390</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540512</t>
+          <t xml:space="preserve">311545404</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-12</t>
+          <t xml:space="preserve">2031-09-02</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -10106,30 +10106,30 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkestræde 24</t>
+          <t xml:space="preserve">Lidemarksvej 97D</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4632</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">8948780</t>
+          <t xml:space="preserve">2589978</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H156">
-        <v>253</v>
+        <v>390</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540512</t>
+          <t xml:space="preserve">311545404</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-12</t>
+          <t xml:space="preserve">2031-09-02</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -10171,30 +10171,30 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gemsevej 19</t>
+          <t xml:space="preserve">Lidemarksvej 97G</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">4623</t>
+          <t xml:space="preserve">4632</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2212648</t>
+          <t xml:space="preserve">2589978</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H157">
-        <v>443</v>
+        <v>254</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540701</t>
+          <t xml:space="preserve">311545528</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -10204,7 +10204,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-13</t>
+          <t xml:space="preserve">2031-09-02</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -10236,30 +10236,30 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gymnasievej 8</t>
+          <t xml:space="preserve">Vemmedrupvej 235</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4632</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">100040993</t>
+          <t xml:space="preserve">2590529</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H158">
-        <v>756</v>
+        <v>590</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311543562</t>
+          <t xml:space="preserve">311549276</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -10269,7 +10269,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-26</t>
+          <t xml:space="preserve">2031-09-20</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fændediget 4</t>
+          <t xml:space="preserve">Vestergade 3A</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -10311,20 +10311,20 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">5299406</t>
+          <t xml:space="preserve">5298617</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H159">
-        <v>481</v>
+        <v>386</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311544545</t>
+          <t xml:space="preserve">311549360</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-31</t>
+          <t xml:space="preserve">2031-09-20</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvang 6</t>
+          <t xml:space="preserve">Buen 21</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -10376,20 +10376,20 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940846</t>
+          <t xml:space="preserve">2214735</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H160">
-        <v>8394</v>
+        <v>416</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311544560</t>
+          <t xml:space="preserve">311550074</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -10399,7 +10399,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-31</t>
+          <t xml:space="preserve">2031-09-22</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -10431,30 +10431,30 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lidemarksvej 97A</t>
+          <t xml:space="preserve">Buen 7</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t xml:space="preserve">4632</t>
+          <t xml:space="preserve">4623</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2589978</t>
+          <t xml:space="preserve">2214735</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H161">
-        <v>390</v>
+        <v>312</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311545404</t>
+          <t xml:space="preserve">311550074</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -10464,7 +10464,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-02</t>
+          <t xml:space="preserve">2031-09-22</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -10496,30 +10496,30 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lidemarksvej 97D</t>
+          <t xml:space="preserve">Ølbycenter 104</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t xml:space="preserve">4632</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2589978</t>
+          <t xml:space="preserve">9223091</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H162">
-        <v>390</v>
+        <v>5045</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311545404</t>
+          <t xml:space="preserve">311550306</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -10529,7 +10529,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-02</t>
+          <t xml:space="preserve">2031-09-23</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -10561,7 +10561,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lidemarksvej 97G</t>
+          <t xml:space="preserve">Halvejen 2</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10576,15 +10576,15 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H163">
-        <v>254</v>
+        <v>6715</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311545528</t>
+          <t xml:space="preserve">311561871</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-02</t>
+          <t xml:space="preserve">2031-11-15</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vemmedrupvej 235</t>
+          <t xml:space="preserve">Halvejen 2</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -10636,20 +10636,20 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2590529</t>
+          <t xml:space="preserve">2589978</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H164">
-        <v>590</v>
+        <v>2017</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549276</t>
+          <t xml:space="preserve">311561871</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -10659,7 +10659,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-20</t>
+          <t xml:space="preserve">2031-11-15</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -10691,30 +10691,30 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 3A</t>
+          <t xml:space="preserve">Halvejen 2</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4632</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298617</t>
+          <t xml:space="preserve">2589978</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H165">
-        <v>386</v>
+        <v>1359</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549360</t>
+          <t xml:space="preserve">311561871</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-20</t>
+          <t xml:space="preserve">2031-11-15</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -10756,30 +10756,30 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buen 21</t>
+          <t xml:space="preserve">Møllevej 2</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve">4623</t>
+          <t xml:space="preserve">4140</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2214735</t>
+          <t xml:space="preserve">100013861</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H166">
-        <v>416</v>
+        <v>3292</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311550074</t>
+          <t xml:space="preserve">311566593</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-22</t>
+          <t xml:space="preserve">2031-12-07</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -10821,17 +10821,17 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buen 7</t>
+          <t xml:space="preserve">Karlemosevej 48</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">4623</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2214735</t>
+          <t xml:space="preserve">2215842</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -10840,11 +10840,11 @@
         </is>
       </c>
       <c r="H167">
-        <v>312</v>
+        <v>676</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311550074</t>
+          <t xml:space="preserve">311568002</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-22</t>
+          <t xml:space="preserve">2031-12-15</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ølbycenter 104</t>
+          <t xml:space="preserve">Torvet 1</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10896,20 +10896,20 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">9223091</t>
+          <t xml:space="preserve">266956, 266957</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H168">
-        <v>5045</v>
+        <v>7502</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311550306</t>
+          <t xml:space="preserve">311570444</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-23</t>
+          <t xml:space="preserve">2032-01-04</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -10951,30 +10951,30 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halvejen 2</t>
+          <t xml:space="preserve">Torvet 1</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t xml:space="preserve">4632</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2589978</t>
+          <t xml:space="preserve">266956, 266958</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H169">
-        <v>6715</v>
+        <v>4799</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561871</t>
+          <t xml:space="preserve">311570444</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -10984,7 +10984,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-15</t>
+          <t xml:space="preserve">2032-01-04</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -11016,30 +11016,30 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halvejen 2</t>
+          <t xml:space="preserve">Søbækvej 2</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t xml:space="preserve">4632</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2589978</t>
+          <t xml:space="preserve">9492257</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H170">
-        <v>2017</v>
+        <v>856</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561871</t>
+          <t xml:space="preserve">311571109</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-15</t>
+          <t xml:space="preserve">2032-01-07</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -11081,30 +11081,30 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halvejen 2</t>
+          <t xml:space="preserve">Rasmussensvej 23</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t xml:space="preserve">4632</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2589978</t>
+          <t xml:space="preserve">8314862</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H171">
-        <v>1359</v>
+        <v>4490</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561871</t>
+          <t xml:space="preserve">311574331</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -11114,7 +11114,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-15</t>
+          <t xml:space="preserve">2032-01-25</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -11146,17 +11146,17 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevej 2</t>
+          <t xml:space="preserve">Gymnasievej 10</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t xml:space="preserve">4140</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">100013861</t>
+          <t xml:space="preserve">5301791</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -11165,11 +11165,11 @@
         </is>
       </c>
       <c r="H172">
-        <v>3292</v>
+        <v>5745</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566593</t>
+          <t xml:space="preserve">311574812</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -11179,7 +11179,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-07</t>
+          <t xml:space="preserve">2032-01-26</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karlemosevej 48</t>
+          <t xml:space="preserve">Gymnasievej 10</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -11221,20 +11221,20 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2215842</t>
+          <t xml:space="preserve">5301791</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H173">
-        <v>676</v>
+        <v>1353</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568002</t>
+          <t xml:space="preserve">311574812</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -11244,7 +11244,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-15</t>
+          <t xml:space="preserve">2032-01-26</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -11276,30 +11276,30 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvet 1</t>
+          <t xml:space="preserve">Jernhøj 1</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4140</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">266956, 266957</t>
+          <t xml:space="preserve">100041898</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H174">
-        <v>7502</v>
+        <v>2276</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311570444</t>
+          <t xml:space="preserve">311575628</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-04</t>
+          <t xml:space="preserve">2032-01-31</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvet 1</t>
+          <t xml:space="preserve">Skolevej 1</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -11351,20 +11351,20 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">266956, 266958</t>
+          <t xml:space="preserve">2219385</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H175">
-        <v>4799</v>
+        <v>1776</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311570444</t>
+          <t xml:space="preserve">311578008</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -11374,7 +11374,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-04</t>
+          <t xml:space="preserve">2032-02-10</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -11406,7 +11406,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søbækvej 2</t>
+          <t xml:space="preserve">Skolevej 1</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -11416,20 +11416,20 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">9492257</t>
+          <t xml:space="preserve">2219385</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H176">
-        <v>856</v>
+        <v>701</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571109</t>
+          <t xml:space="preserve">311578008</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -11439,7 +11439,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-07</t>
+          <t xml:space="preserve">2032-02-10</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -11471,7 +11471,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rasmussensvej 23</t>
+          <t xml:space="preserve">Skolevej 1</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -11481,20 +11481,20 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">8314862</t>
+          <t xml:space="preserve">2219385</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H177">
-        <v>4490</v>
+        <v>1695</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311574331</t>
+          <t xml:space="preserve">311578008</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -11504,7 +11504,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-25</t>
+          <t xml:space="preserve">2032-02-10</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -11536,7 +11536,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gymnasievej 10</t>
+          <t xml:space="preserve">Skolevej 1</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -11546,20 +11546,20 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">5301791</t>
+          <t xml:space="preserve">2219385</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H178">
-        <v>5745</v>
+        <v>933</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311574812</t>
+          <t xml:space="preserve">311578008</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -11569,7 +11569,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-26</t>
+          <t xml:space="preserve">2032-02-10</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -11601,7 +11601,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gymnasievej 10</t>
+          <t xml:space="preserve">Skolevej 1</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -11611,20 +11611,20 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">5301791</t>
+          <t xml:space="preserve">2219385</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H179">
-        <v>1353</v>
+        <v>966</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311574812</t>
+          <t xml:space="preserve">311578008</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-26</t>
+          <t xml:space="preserve">2032-02-10</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -11666,30 +11666,30 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernhøj 1</t>
+          <t xml:space="preserve">Skolevej 1</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve">4140</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">100041898</t>
+          <t xml:space="preserve">2219385</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H180">
-        <v>2276</v>
+        <v>1139</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311575628</t>
+          <t xml:space="preserve">311578008</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-31</t>
+          <t xml:space="preserve">2032-02-10</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -11746,11 +11746,11 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H181">
-        <v>1776</v>
+        <v>846</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
@@ -11796,30 +11796,30 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 1</t>
+          <t xml:space="preserve">Vindegårdsvej 1</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4632</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2219385</t>
+          <t xml:space="preserve">8940960</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H182">
-        <v>701</v>
+        <v>4713</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311578008</t>
+          <t xml:space="preserve">311582210</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -11829,7 +11829,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-10</t>
+          <t xml:space="preserve">2032-03-03</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -11861,30 +11861,30 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 1</t>
+          <t xml:space="preserve">Vindegårdsvej 1</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4632</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2219385</t>
+          <t xml:space="preserve">8940960</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H183">
-        <v>1695</v>
+        <v>629</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311578008</t>
+          <t xml:space="preserve">311582210</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -11894,7 +11894,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-10</t>
+          <t xml:space="preserve">2032-03-03</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 1</t>
+          <t xml:space="preserve">Allegade 2A</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -11936,20 +11936,20 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2219385</t>
+          <t xml:space="preserve">5298857</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H184">
-        <v>933</v>
+        <v>972</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311578008</t>
+          <t xml:space="preserve">311583248</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -11959,7 +11959,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-10</t>
+          <t xml:space="preserve">2032-03-08</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 1</t>
+          <t xml:space="preserve">Kirkestræde 28</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -12001,20 +12001,20 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2219385</t>
+          <t xml:space="preserve">5298849</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H185">
-        <v>966</v>
+        <v>876</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311578008</t>
+          <t xml:space="preserve">311583573</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -12024,7 +12024,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-10</t>
+          <t xml:space="preserve">2032-03-09</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -12056,7 +12056,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 1</t>
+          <t xml:space="preserve">Nørregade 43</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -12066,20 +12066,20 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2219385</t>
+          <t xml:space="preserve">5298858</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H186">
-        <v>1139</v>
+        <v>1657</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311578008</t>
+          <t xml:space="preserve">311583564</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-10</t>
+          <t xml:space="preserve">2032-03-09</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -12121,7 +12121,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 1</t>
+          <t xml:space="preserve">Nørregade 43</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -12131,20 +12131,20 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2219385</t>
+          <t xml:space="preserve">5298858</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H187">
-        <v>846</v>
+        <v>1651</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311578008</t>
+          <t xml:space="preserve">311583564</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -12154,7 +12154,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-10</t>
+          <t xml:space="preserve">2032-03-09</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -12186,30 +12186,30 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vindegårdsvej 1</t>
+          <t xml:space="preserve">Lerbæk Torv 30</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t xml:space="preserve">4632</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940960</t>
+          <t xml:space="preserve">268650, 268651</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H188">
-        <v>4713</v>
+        <v>1122</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582210</t>
+          <t xml:space="preserve">311584438</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -12219,7 +12219,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-03</t>
+          <t xml:space="preserve">2032-03-11</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -12251,30 +12251,30 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vindegårdsvej 1</t>
+          <t xml:space="preserve">Sygehusvej 25</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t xml:space="preserve">4632</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940960</t>
+          <t xml:space="preserve">5298996</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H189">
-        <v>629</v>
+        <v>499</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582210</t>
+          <t xml:space="preserve">311584350</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-03</t>
+          <t xml:space="preserve">2032-03-11</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -12316,7 +12316,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allegade 2A</t>
+          <t xml:space="preserve">Sygehusvej 25</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -12326,20 +12326,20 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298857</t>
+          <t xml:space="preserve">5298996</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H190">
-        <v>972</v>
+        <v>347</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311583248</t>
+          <t xml:space="preserve">311584350</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -12349,7 +12349,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-08</t>
+          <t xml:space="preserve">2032-03-11</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkestræde 28</t>
+          <t xml:space="preserve">Sygehusvej 25</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -12391,20 +12391,20 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298849</t>
+          <t xml:space="preserve">5298996</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H191">
-        <v>876</v>
+        <v>800</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311583573</t>
+          <t xml:space="preserve">311584350</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -12414,7 +12414,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-09</t>
+          <t xml:space="preserve">2032-03-11</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -12446,7 +12446,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 43</t>
+          <t xml:space="preserve">Københavnsvej 265</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -12456,20 +12456,20 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298858</t>
+          <t xml:space="preserve">8195911</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H192">
-        <v>1657</v>
+        <v>292</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311583564</t>
+          <t xml:space="preserve">311586697</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-09</t>
+          <t xml:space="preserve">2032-03-21</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -12511,7 +12511,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 43</t>
+          <t xml:space="preserve">Nylandsvej 115</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -12521,20 +12521,20 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298858</t>
+          <t xml:space="preserve">8013178</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H193">
-        <v>1651</v>
+        <v>418</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311583564</t>
+          <t xml:space="preserve">311597197</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-09</t>
+          <t xml:space="preserve">2032-05-03</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -12576,7 +12576,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerbæk Torv 30</t>
+          <t xml:space="preserve">Nylandsvej 117</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -12586,20 +12586,20 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">268650, 268651</t>
+          <t xml:space="preserve">8013178</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H194">
-        <v>1122</v>
+        <v>350</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311584438</t>
+          <t xml:space="preserve">311597197</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -12609,7 +12609,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-11</t>
+          <t xml:space="preserve">2032-05-03</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sygehusvej 25</t>
+          <t xml:space="preserve">Ved Stadion 10</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -12651,20 +12651,20 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298996</t>
+          <t xml:space="preserve">265103</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H195">
-        <v>499</v>
+        <v>298</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311584350</t>
+          <t xml:space="preserve">311597207</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -12674,7 +12674,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-11</t>
+          <t xml:space="preserve">2032-05-03</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -12706,7 +12706,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sygehusvej 25</t>
+          <t xml:space="preserve">Fuglebæk Alle 3</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -12716,30 +12716,30 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298996</t>
+          <t xml:space="preserve">100090478</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H196">
-        <v>347</v>
+        <v>2788</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311584350</t>
+          <t xml:space="preserve">311626787</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t xml:space="preserve">EWII Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-11</t>
+          <t xml:space="preserve">2032-09-09</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -12771,7 +12771,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sygehusvej 25</t>
+          <t xml:space="preserve">Bag Haverne 1</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -12781,30 +12781,30 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">5298996</t>
+          <t xml:space="preserve">5299445</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H197">
-        <v>800</v>
+        <v>1589</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311584350</t>
+          <t xml:space="preserve">311637067</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t xml:space="preserve">EWII Energi A/S</t>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-11</t>
+          <t xml:space="preserve">2032-10-20</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Københavnsvej 265</t>
+          <t xml:space="preserve">Rishøjvej 1C</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -12846,30 +12846,30 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">8195911</t>
+          <t xml:space="preserve">2219342</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H198">
-        <v>292</v>
+        <v>1190</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586697</t>
+          <t xml:space="preserve">311719130</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t xml:space="preserve">EWII Energi A/S</t>
+          <t xml:space="preserve">Inspec ApS</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-21</t>
+          <t xml:space="preserve">2033-11-01</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -12901,7 +12901,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nylandsvej 115</t>
+          <t xml:space="preserve">Ravnsborgvej 3D</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -12911,7 +12911,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">8013178</t>
+          <t xml:space="preserve">8960384</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -12920,21 +12920,21 @@
         </is>
       </c>
       <c r="H199">
-        <v>418</v>
+        <v>1820</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311597197</t>
+          <t xml:space="preserve">311724352</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t xml:space="preserve">EWII Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-03</t>
+          <t xml:space="preserve">2033-11-23</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -12966,40 +12966,40 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nylandsvej 117</t>
+          <t xml:space="preserve">Bjæverskovhusene 34</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4632</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">8013178</t>
+          <t xml:space="preserve">271380, 271381</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H200">
-        <v>350</v>
+        <v>1104</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311597197</t>
+          <t xml:space="preserve">311725609</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t xml:space="preserve">EWII Energi A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-03</t>
+          <t xml:space="preserve">2033-11-29</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -13031,17 +13031,17 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Stadion 10</t>
+          <t xml:space="preserve">Møllevej 4B</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4140</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">265103</t>
+          <t xml:space="preserve">2209946</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -13050,21 +13050,21 @@
         </is>
       </c>
       <c r="H201">
-        <v>298</v>
+        <v>4800</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311597207</t>
+          <t xml:space="preserve">311731961</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t xml:space="preserve">EWII Energi A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-03</t>
+          <t xml:space="preserve">2034-01-05</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglebæk Alle 3</t>
+          <t xml:space="preserve">Værkstedsvej 3</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -13106,7 +13106,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">100090478</t>
+          <t xml:space="preserve">2218588</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -13115,21 +13115,21 @@
         </is>
       </c>
       <c r="H202">
-        <v>2788</v>
+        <v>1711</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311626787</t>
+          <t xml:space="preserve">311777229</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-09</t>
+          <t xml:space="preserve">2034-08-09</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -13161,7 +13161,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bag Haverne 1</t>
+          <t xml:space="preserve">Ved Stadion 1</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -13171,30 +13171,30 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">5299445</t>
+          <t xml:space="preserve">5300128</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H203">
-        <v>1589</v>
+        <v>1050</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311637067</t>
+          <t xml:space="preserve">311846132</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve">Norca Aps</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-20</t>
+          <t xml:space="preserve">2035-07-24</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -13226,30 +13226,30 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rishøjvej 1C</t>
+          <t xml:space="preserve">Lundegårdsvej 2</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t xml:space="preserve">4600</t>
+          <t xml:space="preserve">4100</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2219342</t>
+          <t xml:space="preserve">2591592</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="H204">
-        <v>1190</v>
+        <v>290</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719130</t>
+          <t xml:space="preserve">311859345</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -13259,7 +13259,7 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-01</t>
+          <t xml:space="preserve">2035-10-01</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -13291,7 +13291,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnsborgvej 3D</t>
+          <t xml:space="preserve">Byledet 66</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">8960384</t>
+          <t xml:space="preserve">5302818</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -13310,21 +13310,21 @@
         </is>
       </c>
       <c r="H205">
-        <v>1820</v>
+        <v>529</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311724352</t>
+          <t xml:space="preserve">311918710</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-23</t>
+          <t xml:space="preserve">2036-08-12</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -13356,30 +13356,30 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjæverskovhusene 34</t>
+          <t xml:space="preserve">Tigervej 8</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t xml:space="preserve">4632</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">271380, 271381</t>
+          <t xml:space="preserve">5300146</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H206">
-        <v>1104</v>
+        <v>309</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725609</t>
+          <t xml:space="preserve">311918711</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -13389,7 +13389,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-29</t>
+          <t xml:space="preserve">2036-08-12</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -13421,30 +13421,30 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevej 4B</t>
+          <t xml:space="preserve">Tigervej 8</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t xml:space="preserve">4140</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209946</t>
+          <t xml:space="preserve">5300146</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H207">
-        <v>4800</v>
+        <v>1034</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311731961</t>
+          <t xml:space="preserve">311918712</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-05</t>
+          <t xml:space="preserve">2036-08-12</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -13486,7 +13486,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Værkstedsvej 3</t>
+          <t xml:space="preserve">Norsvej 2</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -13496,7 +13496,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2218588</t>
+          <t xml:space="preserve">8765343</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -13505,11 +13505,11 @@
         </is>
       </c>
       <c r="H208">
-        <v>1711</v>
+        <v>2988</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311777229</t>
+          <t xml:space="preserve">311924059</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -13519,7 +13519,7 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-09</t>
+          <t xml:space="preserve">2036-09-07</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -13551,7 +13551,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Stadion 1</t>
+          <t xml:space="preserve">Norsvej 2</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -13561,7 +13561,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">5300128</t>
+          <t xml:space="preserve">8765343</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -13570,21 +13570,21 @@
         </is>
       </c>
       <c r="H209">
-        <v>1050</v>
+        <v>2512</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311846132</t>
+          <t xml:space="preserve">311924059</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norca Aps</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-24</t>
+          <t xml:space="preserve">2036-09-07</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -13616,40 +13616,40 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundegårdsvej 2</t>
+          <t xml:space="preserve">Norsvej 2</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t xml:space="preserve">4100</t>
+          <t xml:space="preserve">4600</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2591592</t>
+          <t xml:space="preserve">8765343</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H210">
-        <v>290</v>
+        <v>1540</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311859345</t>
+          <t xml:space="preserve">311924059</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspec ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-01</t>
+          <t xml:space="preserve">2036-09-07</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byledet 66</t>
+          <t xml:space="preserve">Norsvej 2</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -13691,20 +13691,20 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">5302818</t>
+          <t xml:space="preserve">8765343</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H211">
-        <v>529</v>
+        <v>2844</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918710</t>
+          <t xml:space="preserve">311924059</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -13714,7 +13714,7 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-12</t>
+          <t xml:space="preserve">2036-09-07</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -13746,7 +13746,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tigervej 8</t>
+          <t xml:space="preserve">Norsvej 2</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -13756,20 +13756,20 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">5300146</t>
+          <t xml:space="preserve">8765343</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H212">
-        <v>309</v>
+        <v>1874</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918714</t>
+          <t xml:space="preserve">311924055</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-12</t>
+          <t xml:space="preserve">2036-09-07</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -13811,7 +13811,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tigervej 8</t>
+          <t xml:space="preserve">Norsvej 6</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -13821,20 +13821,20 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">5300146</t>
+          <t xml:space="preserve">8769222</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H213">
-        <v>1034</v>
+        <v>987</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918712</t>
+          <t xml:space="preserve">311924065</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -13844,7 +13844,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-12</t>
+          <t xml:space="preserve">2036-09-07</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
